--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128734270</v>
+        <v>128743260</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>56871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569991</v>
+        <v>569945</v>
       </c>
       <c r="R2" t="n">
-        <v>6958010</v>
+        <v>6957777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,49 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128735312</v>
+        <v>128735449</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>91466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569958</v>
+        <v>570013</v>
       </c>
       <c r="R3" t="n">
-        <v>6957882</v>
+        <v>6957861</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128735128</v>
+        <v>128734270</v>
       </c>
       <c r="B4" t="n">
         <v>80194</v>
@@ -913,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569944</v>
+        <v>569991</v>
       </c>
       <c r="R4" t="n">
-        <v>6957901</v>
+        <v>6958010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735449</v>
+        <v>128735128</v>
       </c>
       <c r="B5" t="n">
-        <v>91466</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570013</v>
+        <v>569944</v>
       </c>
       <c r="R5" t="n">
-        <v>6957861</v>
+        <v>6957901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128743260</v>
+        <v>128735312</v>
       </c>
       <c r="B6" t="n">
-        <v>56871</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569945</v>
+        <v>569958</v>
       </c>
       <c r="R6" t="n">
-        <v>6957777</v>
+        <v>6957882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,7 +1177,7 @@
         <v>128735195</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128736388</v>
+        <v>128734997</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,43 +1291,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569956</v>
+        <v>569924</v>
       </c>
       <c r="R8" t="n">
-        <v>6957806</v>
+        <v>6957926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,11 +1351,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Slagsmål, 2 Tretåiga hackspettar slåss. Efter flög dom åt varsitt håll och började Trumma båda två!</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,10 +1377,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128734997</v>
+        <v>128736388</v>
       </c>
       <c r="B9" t="n">
-        <v>80194</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,34 +1388,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569924</v>
+        <v>569956</v>
       </c>
       <c r="R9" t="n">
-        <v>6957926</v>
+        <v>6957806</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,6 +1457,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Slagsmål, 2 Tretåiga hackspettar slåss. Efter flög dom åt varsitt håll och började Trumma båda två!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,38 +1595,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128735512</v>
+        <v>128735507</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1635,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569846</v>
+        <v>570013</v>
       </c>
       <c r="R11" t="n">
-        <v>6957795</v>
+        <v>6957861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,11 +1670,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1702,37 +1696,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128735507</v>
+        <v>128735512</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1741,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570013</v>
+        <v>569846</v>
       </c>
       <c r="R12" t="n">
-        <v>6957861</v>
+        <v>6957795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,6 +1772,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2191,7 +2191,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128736601</v>
+        <v>128743248</v>
       </c>
       <c r="B17" t="n">
         <v>57689</v>
@@ -2220,21 +2220,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569845</v>
+        <v>569853</v>
       </c>
       <c r="R17" t="n">
-        <v>6957673</v>
+        <v>6957734</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,7 +2266,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,7 +2293,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128743248</v>
+        <v>128736601</v>
       </c>
       <c r="B18" t="n">
         <v>57689</v>
@@ -2327,16 +2322,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569853</v>
+        <v>569845</v>
       </c>
       <c r="R18" t="n">
-        <v>6957734</v>
+        <v>6957673</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,7 +2505,7 @@
         <v>128735623</v>
       </c>
       <c r="B20" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2608,37 +2608,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128733844</v>
+        <v>128735562</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2647,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569954</v>
+        <v>569865</v>
       </c>
       <c r="R21" t="n">
-        <v>6958059</v>
+        <v>6957790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2687,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 exemplar har blommat</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2821,38 +2822,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128735562</v>
+        <v>128733844</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569865</v>
+        <v>569954</v>
       </c>
       <c r="R23" t="n">
-        <v>6957790</v>
+        <v>6958059</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 exemplar har blommat</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,7 +3242,7 @@
         <v>128733310</v>
       </c>
       <c r="B27" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>128733449</v>
       </c>
       <c r="B28" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>128733496</v>
       </c>
       <c r="B30" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128733395</v>
+        <v>128735659</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3650,43 +3650,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569945</v>
+        <v>570026</v>
       </c>
       <c r="R31" t="n">
-        <v>6958015</v>
+        <v>6957897</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3736,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128737501</v>
+        <v>128734061</v>
       </c>
       <c r="B32" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,34 +3747,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569789</v>
+        <v>569997</v>
       </c>
       <c r="R32" t="n">
-        <v>6957820</v>
+        <v>6958070</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3816,6 +3812,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3842,7 +3843,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128734061</v>
+        <v>128733395</v>
       </c>
       <c r="B33" t="n">
         <v>57689</v>
@@ -3870,10 +3871,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3882,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569997</v>
+        <v>569945</v>
       </c>
       <c r="R33" t="n">
-        <v>6958070</v>
+        <v>6958015</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3918,11 +3923,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128735659</v>
+        <v>128737501</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>91484</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>570026</v>
+        <v>569789</v>
       </c>
       <c r="R34" t="n">
-        <v>6957897</v>
+        <v>6957820</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128735869</v>
+        <v>128735254</v>
       </c>
       <c r="B40" t="n">
         <v>80194</v>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569825</v>
+        <v>569890</v>
       </c>
       <c r="R40" t="n">
-        <v>6957814</v>
+        <v>6957854</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4643,49 +4643,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128734316</v>
+        <v>128735869</v>
       </c>
       <c r="B41" t="n">
-        <v>98588</v>
+        <v>80194</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569991</v>
+        <v>569825</v>
       </c>
       <c r="R41" t="n">
-        <v>6958010</v>
+        <v>6957814</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4718,11 +4714,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4856,45 +4847,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128735254</v>
+        <v>128734316</v>
       </c>
       <c r="B43" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569890</v>
+        <v>569991</v>
       </c>
       <c r="R43" t="n">
-        <v>6957854</v>
+        <v>6958010</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4927,6 +4922,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4956,7 +4956,7 @@
         <v>128733519</v>
       </c>
       <c r="B44" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>128743259</v>
       </c>
       <c r="B45" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128737653</v>
+        <v>128735020</v>
       </c>
       <c r="B46" t="n">
         <v>80229</v>
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569789</v>
+        <v>569908</v>
       </c>
       <c r="R46" t="n">
-        <v>6957820</v>
+        <v>6957928</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5258,7 +5258,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128735020</v>
+        <v>128737653</v>
       </c>
       <c r="B47" t="n">
         <v>80229</v>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569908</v>
+        <v>569789</v>
       </c>
       <c r="R47" t="n">
-        <v>6957928</v>
+        <v>6957820</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5465,7 +5465,7 @@
         <v>128743258</v>
       </c>
       <c r="B49" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -3639,10 +3639,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128735659</v>
+        <v>128737501</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>91484</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3650,21 +3650,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>570026</v>
+        <v>569789</v>
       </c>
       <c r="R31" t="n">
-        <v>6957897</v>
+        <v>6957820</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3736,10 +3736,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128734061</v>
+        <v>128735659</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3747,39 +3747,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569997</v>
+        <v>570026</v>
       </c>
       <c r="R32" t="n">
-        <v>6958070</v>
+        <v>6957897</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3812,11 +3807,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3843,7 +3833,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128733395</v>
+        <v>128734061</v>
       </c>
       <c r="B33" t="n">
         <v>57689</v>
@@ -3871,14 +3861,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3887,10 +3873,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569945</v>
+        <v>569997</v>
       </c>
       <c r="R33" t="n">
-        <v>6958015</v>
+        <v>6958070</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3923,6 +3909,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3949,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128737501</v>
+        <v>128733395</v>
       </c>
       <c r="B34" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3960,34 +3951,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569789</v>
+        <v>569945</v>
       </c>
       <c r="R34" t="n">
-        <v>6957820</v>
+        <v>6958015</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128743260</v>
+        <v>128735449</v>
       </c>
       <c r="B2" t="n">
-        <v>56871</v>
+        <v>91467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569945</v>
+        <v>570013</v>
       </c>
       <c r="R2" t="n">
-        <v>6957777</v>
+        <v>6957861</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128735449</v>
+        <v>128734270</v>
       </c>
       <c r="B3" t="n">
-        <v>91466</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570013</v>
+        <v>569991</v>
       </c>
       <c r="R3" t="n">
-        <v>6957861</v>
+        <v>6958010</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128734270</v>
+        <v>128735128</v>
       </c>
       <c r="B4" t="n">
         <v>80194</v>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569991</v>
+        <v>569944</v>
       </c>
       <c r="R4" t="n">
-        <v>6958010</v>
+        <v>6957901</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,45 +966,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735128</v>
+        <v>128735312</v>
       </c>
       <c r="B5" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569944</v>
+        <v>569958</v>
       </c>
       <c r="R5" t="n">
-        <v>6957901</v>
+        <v>6957882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1041,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,49 +1072,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128735312</v>
+        <v>128743260</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>56871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569958</v>
+        <v>569945</v>
       </c>
       <c r="R6" t="n">
-        <v>6957882</v>
+        <v>6957777</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ett exemplar har blommat</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,7 +1177,7 @@
         <v>128735195</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128736388</v>
+        <v>128735394</v>
       </c>
       <c r="B9" t="n">
         <v>57689</v>
@@ -1405,14 +1405,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1421,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569956</v>
+        <v>569866</v>
       </c>
       <c r="R9" t="n">
-        <v>6957806</v>
+        <v>6957856</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,7 +1457,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Slagsmål, 2 Tretåiga hackspettar slåss. Efter flög dom åt varsitt håll och började Trumma båda två!</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,38 +1484,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128735394</v>
+        <v>128735507</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569866</v>
+        <v>570013</v>
       </c>
       <c r="R10" t="n">
-        <v>6957856</v>
+        <v>6957861</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,11 +1559,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,37 +1585,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128735507</v>
+        <v>128735512</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1634,10 +1625,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570013</v>
+        <v>569846</v>
       </c>
       <c r="R11" t="n">
-        <v>6957861</v>
+        <v>6957795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1670,6 +1661,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1696,50 +1692,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128735512</v>
+        <v>128734913</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>80223</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569846</v>
+        <v>569924</v>
       </c>
       <c r="R12" t="n">
-        <v>6957795</v>
+        <v>6957910</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1772,11 +1763,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1803,32 +1789,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128735988</v>
+        <v>128736431</v>
       </c>
       <c r="B13" t="n">
-        <v>91484</v>
+        <v>80223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1838,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569802</v>
+        <v>569829</v>
       </c>
       <c r="R13" t="n">
-        <v>6957819</v>
+        <v>6957746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,32 +1886,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128734913</v>
+        <v>128736020</v>
       </c>
       <c r="B14" t="n">
-        <v>80223</v>
+        <v>80194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569924</v>
+        <v>569789</v>
       </c>
       <c r="R14" t="n">
-        <v>6957910</v>
+        <v>6957820</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,32 +1983,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128736431</v>
+        <v>128735988</v>
       </c>
       <c r="B15" t="n">
-        <v>80223</v>
+        <v>91485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2032,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569829</v>
+        <v>569802</v>
       </c>
       <c r="R15" t="n">
-        <v>6957746</v>
+        <v>6957819</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128736020</v>
+        <v>128743248</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2129,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569789</v>
+        <v>569853</v>
       </c>
       <c r="R16" t="n">
-        <v>6957820</v>
+        <v>6957734</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,6 +2151,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2191,7 +2182,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128743248</v>
+        <v>128736601</v>
       </c>
       <c r="B17" t="n">
         <v>57689</v>
@@ -2220,16 +2211,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569853</v>
+        <v>569845</v>
       </c>
       <c r="R17" t="n">
-        <v>6957734</v>
+        <v>6957673</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2266,7 +2262,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2293,10 +2289,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128736601</v>
+        <v>128743249</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>57849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2304,39 +2300,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569845</v>
+        <v>569769</v>
       </c>
       <c r="R18" t="n">
-        <v>6957673</v>
+        <v>6957830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2373,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,45 +2391,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128743249</v>
+        <v>128735623</v>
       </c>
       <c r="B19" t="n">
-        <v>57849</v>
+        <v>98592</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569769</v>
+        <v>570026</v>
       </c>
       <c r="R19" t="n">
-        <v>6957830</v>
+        <v>6957884</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,7 +2470,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Troligt att det finns fler gömda i blåbärsriset/mosan</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2502,10 +2497,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128735623</v>
+        <v>128733844</v>
       </c>
       <c r="B20" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,7 +2527,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2541,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570026</v>
+        <v>569954</v>
       </c>
       <c r="R20" t="n">
-        <v>6957884</v>
+        <v>6958059</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Troligt att det finns fler gömda i blåbärsriset/mosan</t>
+          <t>1 exemplar har blommat</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,37 +2817,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128733844</v>
+        <v>128735718</v>
       </c>
       <c r="B23" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2861,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569954</v>
+        <v>569857</v>
       </c>
       <c r="R23" t="n">
-        <v>6958059</v>
+        <v>6957746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2901,7 +2897,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 exemplar har blommat</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2928,45 +2924,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128735901</v>
+        <v>128733608</v>
       </c>
       <c r="B24" t="n">
-        <v>91431</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569825</v>
+        <v>569939</v>
       </c>
       <c r="R24" t="n">
-        <v>6957814</v>
+        <v>6958006</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2999,6 +3000,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3025,50 +3031,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128733608</v>
+        <v>128743251</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>97463</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569939</v>
+        <v>569826</v>
       </c>
       <c r="R25" t="n">
-        <v>6958006</v>
+        <v>6957739</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3101,11 +3102,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3132,50 +3128,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128735718</v>
+        <v>128735901</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>91432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569857</v>
+        <v>569825</v>
       </c>
       <c r="R26" t="n">
-        <v>6957746</v>
+        <v>6957814</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3208,11 +3199,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3239,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128733310</v>
+        <v>128733449</v>
       </c>
       <c r="B27" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3269,7 +3255,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3278,10 +3264,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569917</v>
+        <v>569942</v>
       </c>
       <c r="R27" t="n">
-        <v>6958104</v>
+        <v>6958086</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3340,10 +3326,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128733449</v>
+        <v>128733310</v>
       </c>
       <c r="B28" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3370,7 +3356,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3379,10 +3365,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569942</v>
+        <v>569917</v>
       </c>
       <c r="R28" t="n">
-        <v>6958086</v>
+        <v>6958104</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3441,45 +3427,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128743251</v>
+        <v>128733496</v>
       </c>
       <c r="B29" t="n">
-        <v>97462</v>
+        <v>98592</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569826</v>
+        <v>569945</v>
       </c>
       <c r="R29" t="n">
-        <v>6957739</v>
+        <v>6958015</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,37 +3528,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128733496</v>
+        <v>128734061</v>
       </c>
       <c r="B30" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3577,10 +3568,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569945</v>
+        <v>569997</v>
       </c>
       <c r="R30" t="n">
-        <v>6958015</v>
+        <v>6958070</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3613,6 +3604,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3642,7 +3638,7 @@
         <v>128737501</v>
       </c>
       <c r="B31" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,7 +3829,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128734061</v>
+        <v>128735365</v>
       </c>
       <c r="B33" t="n">
         <v>57689</v>
@@ -3873,10 +3869,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569997</v>
+        <v>569970</v>
       </c>
       <c r="R33" t="n">
-        <v>6958070</v>
+        <v>6957886</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3913,7 +3909,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på död tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3940,10 +3936,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128733395</v>
+        <v>128736806</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,43 +3947,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569945</v>
+        <v>569928</v>
       </c>
       <c r="R34" t="n">
-        <v>6958015</v>
+        <v>6957738</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,32 +4033,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128736806</v>
+        <v>128734237</v>
       </c>
       <c r="B35" t="n">
-        <v>91484</v>
+        <v>97463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4068,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569928</v>
+        <v>570054</v>
       </c>
       <c r="R35" t="n">
-        <v>6957738</v>
+        <v>6958051</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,50 +4130,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128735365</v>
+        <v>128735857</v>
       </c>
       <c r="B36" t="n">
-        <v>57689</v>
+        <v>80230</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569970</v>
+        <v>569825</v>
       </c>
       <c r="R36" t="n">
-        <v>6957886</v>
+        <v>6957814</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4219,11 +4201,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4250,45 +4227,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128734237</v>
+        <v>128733359</v>
       </c>
       <c r="B37" t="n">
-        <v>97462</v>
+        <v>57849</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>570054</v>
+        <v>569926</v>
       </c>
       <c r="R37" t="n">
-        <v>6958051</v>
+        <v>6958108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,32 +4329,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128735857</v>
+        <v>128735254</v>
       </c>
       <c r="B38" t="n">
-        <v>80230</v>
+        <v>80194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4382,10 +4364,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569825</v>
+        <v>569890</v>
       </c>
       <c r="R38" t="n">
-        <v>6957814</v>
+        <v>6957854</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4444,10 +4426,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128733359</v>
+        <v>128735869</v>
       </c>
       <c r="B39" t="n">
-        <v>57849</v>
+        <v>80194</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4455,39 +4437,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569926</v>
+        <v>569825</v>
       </c>
       <c r="R39" t="n">
-        <v>6958108</v>
+        <v>6957814</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4546,10 +4523,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128735254</v>
+        <v>128737787</v>
       </c>
       <c r="B40" t="n">
-        <v>80194</v>
+        <v>57689</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4557,34 +4534,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569890</v>
+        <v>569763</v>
       </c>
       <c r="R40" t="n">
-        <v>6957854</v>
+        <v>6957837</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4617,6 +4599,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4643,45 +4630,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128735869</v>
+        <v>128734316</v>
       </c>
       <c r="B41" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569825</v>
+        <v>569991</v>
       </c>
       <c r="R41" t="n">
-        <v>6957814</v>
+        <v>6958010</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4714,6 +4705,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4740,50 +4736,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128737787</v>
+        <v>128743259</v>
       </c>
       <c r="B42" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569763</v>
+        <v>569937</v>
       </c>
       <c r="R42" t="n">
-        <v>6957837</v>
+        <v>6957753</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4820,7 +4811,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>150 stycken ( ca )</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4847,10 +4838,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128734316</v>
+        <v>128733519</v>
       </c>
       <c r="B43" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4877,7 +4868,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4886,10 +4877,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569991</v>
+        <v>569951</v>
       </c>
       <c r="R43" t="n">
-        <v>6958010</v>
+        <v>6958068</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4926,7 +4917,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
+          <t>Ka finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4953,49 +4944,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128733519</v>
+        <v>128735020</v>
       </c>
       <c r="B44" t="n">
-        <v>98591</v>
+        <v>80229</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569951</v>
+        <v>569908</v>
       </c>
       <c r="R44" t="n">
-        <v>6958068</v>
+        <v>6957928</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5028,11 +5015,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ka finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5059,32 +5041,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128743259</v>
+        <v>128737653</v>
       </c>
       <c r="B45" t="n">
-        <v>98591</v>
+        <v>80229</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5094,10 +5076,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569937</v>
+        <v>569789</v>
       </c>
       <c r="R45" t="n">
-        <v>6957753</v>
+        <v>6957820</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5130,11 +5112,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>150 stycken ( ca )</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5161,32 +5138,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128735020</v>
+        <v>128743258</v>
       </c>
       <c r="B46" t="n">
-        <v>80229</v>
+        <v>98592</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5196,10 +5173,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569908</v>
+        <v>569769</v>
       </c>
       <c r="R46" t="n">
-        <v>6957928</v>
+        <v>6957830</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5232,6 +5209,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5258,45 +5240,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128737653</v>
+        <v>128735159</v>
       </c>
       <c r="B47" t="n">
-        <v>80229</v>
+        <v>57689</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569789</v>
+        <v>569925</v>
       </c>
       <c r="R47" t="n">
-        <v>6957820</v>
+        <v>6957856</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5329,6 +5316,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5355,7 +5347,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128735159</v>
+        <v>128736388</v>
       </c>
       <c r="B48" t="n">
         <v>57689</v>
@@ -5383,10 +5375,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5395,10 +5391,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569925</v>
+        <v>569956</v>
       </c>
       <c r="R48" t="n">
-        <v>6957856</v>
+        <v>6957806</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5435,7 +5431,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Slagsmål, 2 Tretåiga hackspettar slåss. Efter flög dom åt varsitt håll och började Trumma båda två!</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5462,45 +5458,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128743258</v>
+        <v>128733395</v>
       </c>
       <c r="B49" t="n">
-        <v>98591</v>
+        <v>57689</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569769</v>
+        <v>569945</v>
       </c>
       <c r="R49" t="n">
-        <v>6957830</v>
+        <v>6958015</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5533,11 +5538,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128735449</v>
       </c>
       <c r="B2" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128734270</v>
+        <v>128743260</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>56898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569991</v>
+        <v>569945</v>
       </c>
       <c r="R3" t="n">
-        <v>6958010</v>
+        <v>6957777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128735128</v>
+        <v>128734270</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569944</v>
+        <v>569991</v>
       </c>
       <c r="R4" t="n">
-        <v>6957901</v>
+        <v>6958010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,49 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735312</v>
+        <v>128735128</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569958</v>
+        <v>569944</v>
       </c>
       <c r="R5" t="n">
-        <v>6957882</v>
+        <v>6957901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128743260</v>
+        <v>128735312</v>
       </c>
       <c r="B6" t="n">
-        <v>56871</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569945</v>
+        <v>569958</v>
       </c>
       <c r="R6" t="n">
-        <v>6957777</v>
+        <v>6957882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,7 +1177,7 @@
         <v>128735195</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128734997</v>
       </c>
       <c r="B8" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128735394</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,37 +1484,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128735507</v>
+        <v>128735512</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1523,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570013</v>
+        <v>569846</v>
       </c>
       <c r="R10" t="n">
-        <v>6957861</v>
+        <v>6957795</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,6 +1560,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1585,38 +1591,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128735512</v>
+        <v>128735507</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1625,10 +1630,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569846</v>
+        <v>570013</v>
       </c>
       <c r="R11" t="n">
-        <v>6957795</v>
+        <v>6957861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,11 +1666,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,7 +1695,7 @@
         <v>128734913</v>
       </c>
       <c r="B12" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>128736431</v>
       </c>
       <c r="B13" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>128736020</v>
       </c>
       <c r="B14" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128735988</v>
       </c>
       <c r="B15" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743248</v>
+        <v>128736601</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,16 +2109,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569853</v>
+        <v>569845</v>
       </c>
       <c r="R16" t="n">
-        <v>6957734</v>
+        <v>6957673</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2160,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,10 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128736601</v>
+        <v>128743249</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>57876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2193,39 +2198,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569845</v>
+        <v>569769</v>
       </c>
       <c r="R17" t="n">
-        <v>6957673</v>
+        <v>6957830</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2289,10 +2289,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128743249</v>
+        <v>128743248</v>
       </c>
       <c r="B18" t="n">
-        <v>57849</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,21 +2300,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569769</v>
+        <v>569853</v>
       </c>
       <c r="R18" t="n">
-        <v>6957830</v>
+        <v>6957734</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,7 +2394,7 @@
         <v>128735623</v>
       </c>
       <c r="B19" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2497,37 +2497,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128733844</v>
+        <v>128735562</v>
       </c>
       <c r="B20" t="n">
-        <v>98592</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2536,10 +2537,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569954</v>
+        <v>569865</v>
       </c>
       <c r="R20" t="n">
-        <v>6958059</v>
+        <v>6957790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2577,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 exemplar har blommat</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2603,10 +2604,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128735562</v>
+        <v>128734344</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,7 +2635,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2643,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569865</v>
+        <v>570110</v>
       </c>
       <c r="R21" t="n">
-        <v>6957790</v>
+        <v>6958034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,38 +2711,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128734344</v>
+        <v>128733844</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570110</v>
+        <v>569954</v>
       </c>
       <c r="R22" t="n">
-        <v>6958034</v>
+        <v>6958059</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 exemplar har blommat</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,50 +2817,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128735718</v>
+        <v>128735901</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>91459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569857</v>
+        <v>569825</v>
       </c>
       <c r="R23" t="n">
-        <v>6957746</v>
+        <v>6957814</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,11 +2888,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,7 +2917,7 @@
         <v>128733608</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3031,45 +3021,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128743251</v>
+        <v>128735718</v>
       </c>
       <c r="B25" t="n">
-        <v>97463</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569826</v>
+        <v>569857</v>
       </c>
       <c r="R25" t="n">
-        <v>6957739</v>
+        <v>6957746</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3102,6 +3097,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128735901</v>
+        <v>128743251</v>
       </c>
       <c r="B26" t="n">
-        <v>91432</v>
+        <v>97490</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569825</v>
+        <v>569826</v>
       </c>
       <c r="R26" t="n">
-        <v>6957814</v>
+        <v>6957739</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128733449</v>
+        <v>128733310</v>
       </c>
       <c r="B27" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569942</v>
+        <v>569917</v>
       </c>
       <c r="R27" t="n">
-        <v>6958086</v>
+        <v>6958104</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,10 +3326,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128733310</v>
+        <v>128733449</v>
       </c>
       <c r="B28" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569917</v>
+        <v>569942</v>
       </c>
       <c r="R28" t="n">
-        <v>6958104</v>
+        <v>6958086</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
         <v>128733496</v>
       </c>
       <c r="B29" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128734061</v>
+        <v>128737501</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>91512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,39 +3539,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569997</v>
+        <v>569789</v>
       </c>
       <c r="R30" t="n">
-        <v>6958070</v>
+        <v>6957820</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3604,11 +3599,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3635,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128737501</v>
+        <v>128735659</v>
       </c>
       <c r="B31" t="n">
-        <v>91485</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3646,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3670,10 +3660,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569789</v>
+        <v>570026</v>
       </c>
       <c r="R31" t="n">
-        <v>6957820</v>
+        <v>6957897</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3732,10 +3722,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128735659</v>
+        <v>128734061</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3743,34 +3733,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>570026</v>
+        <v>569997</v>
       </c>
       <c r="R32" t="n">
-        <v>6957897</v>
+        <v>6958070</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3803,6 +3798,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3829,10 +3829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128735365</v>
+        <v>128736806</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>91512</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,39 +3840,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569970</v>
+        <v>569928</v>
       </c>
       <c r="R33" t="n">
-        <v>6957886</v>
+        <v>6957738</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3905,11 +3900,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,10 +3926,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128736806</v>
+        <v>128735365</v>
       </c>
       <c r="B34" t="n">
-        <v>91485</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,34 +3937,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569928</v>
+        <v>569970</v>
       </c>
       <c r="R34" t="n">
-        <v>6957738</v>
+        <v>6957886</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4007,6 +4002,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4036,7 +4036,7 @@
         <v>128734237</v>
       </c>
       <c r="B35" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>128735857</v>
       </c>
       <c r="B36" t="n">
-        <v>80230</v>
+        <v>80257</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>128733359</v>
       </c>
       <c r="B37" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4329,10 +4329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128735254</v>
+        <v>128737787</v>
       </c>
       <c r="B38" t="n">
-        <v>80194</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,34 +4340,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569890</v>
+        <v>569763</v>
       </c>
       <c r="R38" t="n">
-        <v>6957854</v>
+        <v>6957837</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,6 +4405,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4426,10 +4436,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128735869</v>
+        <v>128735254</v>
       </c>
       <c r="B39" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,10 +4471,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569825</v>
+        <v>569890</v>
       </c>
       <c r="R39" t="n">
-        <v>6957814</v>
+        <v>6957854</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4523,10 +4533,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128737787</v>
+        <v>128735869</v>
       </c>
       <c r="B40" t="n">
-        <v>57689</v>
+        <v>80221</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4534,39 +4544,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569763</v>
+        <v>569825</v>
       </c>
       <c r="R40" t="n">
-        <v>6957837</v>
+        <v>6957814</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4599,11 +4604,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4633,7 +4633,7 @@
         <v>128734316</v>
       </c>
       <c r="B41" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4736,10 +4736,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128743259</v>
+        <v>128733519</v>
       </c>
       <c r="B42" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,17 +4764,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569937</v>
+        <v>569951</v>
       </c>
       <c r="R42" t="n">
-        <v>6957753</v>
+        <v>6958068</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4811,7 +4815,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>150 stycken ( ca )</t>
+          <t>Ka finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4838,10 +4842,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128733519</v>
+        <v>128743259</v>
       </c>
       <c r="B43" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4866,21 +4870,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569951</v>
+        <v>569937</v>
       </c>
       <c r="R43" t="n">
-        <v>6958068</v>
+        <v>6957753</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ka finnas mer I mossan</t>
+          <t>150 stycken ( ca )</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4947,7 +4947,7 @@
         <v>128735020</v>
       </c>
       <c r="B44" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>128737653</v>
       </c>
       <c r="B45" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>128743258</v>
       </c>
       <c r="B46" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>128735159</v>
       </c>
       <c r="B47" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>128736388</v>
       </c>
       <c r="B48" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>128733395</v>
       </c>
       <c r="B49" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128735449</v>
+        <v>128734270</v>
       </c>
       <c r="B2" t="n">
-        <v>91494</v>
+        <v>80221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570013</v>
+        <v>569991</v>
       </c>
       <c r="R2" t="n">
-        <v>6957861</v>
+        <v>6958010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128743260</v>
+        <v>128735128</v>
       </c>
       <c r="B3" t="n">
-        <v>56898</v>
+        <v>80221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569945</v>
+        <v>569944</v>
       </c>
       <c r="R3" t="n">
-        <v>6957777</v>
+        <v>6957901</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128734270</v>
+        <v>128743260</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>56898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569991</v>
+        <v>569945</v>
       </c>
       <c r="R4" t="n">
-        <v>6958010</v>
+        <v>6957777</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,45 +971,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735128</v>
+        <v>128735312</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569944</v>
+        <v>569958</v>
       </c>
       <c r="R5" t="n">
-        <v>6957901</v>
+        <v>6957882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1046,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,49 +1077,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128735312</v>
+        <v>128735449</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>91494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569958</v>
+        <v>570013</v>
       </c>
       <c r="R6" t="n">
-        <v>6957882</v>
+        <v>6957861</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,11 +1148,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1692,32 +1692,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128734913</v>
+        <v>128735988</v>
       </c>
       <c r="B12" t="n">
-        <v>80250</v>
+        <v>91512</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569924</v>
+        <v>569802</v>
       </c>
       <c r="R12" t="n">
-        <v>6957910</v>
+        <v>6957819</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128736431</v>
+        <v>128734913</v>
       </c>
       <c r="B13" t="n">
         <v>80250</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569829</v>
+        <v>569924</v>
       </c>
       <c r="R13" t="n">
-        <v>6957746</v>
+        <v>6957910</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,32 +1886,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128736020</v>
+        <v>128736431</v>
       </c>
       <c r="B14" t="n">
-        <v>80221</v>
+        <v>80250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569789</v>
+        <v>569829</v>
       </c>
       <c r="R14" t="n">
-        <v>6957820</v>
+        <v>6957746</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128735988</v>
+        <v>128736020</v>
       </c>
       <c r="B15" t="n">
-        <v>91512</v>
+        <v>80221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569802</v>
+        <v>569789</v>
       </c>
       <c r="R15" t="n">
-        <v>6957819</v>
+        <v>6957820</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128736601</v>
+        <v>128743248</v>
       </c>
       <c r="B16" t="n">
         <v>57716</v>
@@ -2109,21 +2109,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569845</v>
+        <v>569853</v>
       </c>
       <c r="R16" t="n">
-        <v>6957673</v>
+        <v>6957734</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2187,10 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128743249</v>
+        <v>128736601</v>
       </c>
       <c r="B17" t="n">
-        <v>57876</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2198,34 +2193,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569769</v>
+        <v>569845</v>
       </c>
       <c r="R17" t="n">
-        <v>6957830</v>
+        <v>6957673</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2289,10 +2289,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128743248</v>
+        <v>128743249</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,21 +2300,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569853</v>
+        <v>569769</v>
       </c>
       <c r="R18" t="n">
-        <v>6957734</v>
+        <v>6957830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3128,45 +3128,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128743251</v>
+        <v>128733310</v>
       </c>
       <c r="B26" t="n">
-        <v>97490</v>
+        <v>98619</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569826</v>
+        <v>569917</v>
       </c>
       <c r="R26" t="n">
-        <v>6957739</v>
+        <v>6958104</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,49 +3229,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128733310</v>
+        <v>128743251</v>
       </c>
       <c r="B27" t="n">
-        <v>98619</v>
+        <v>97490</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569917</v>
+        <v>569826</v>
       </c>
       <c r="R27" t="n">
-        <v>6958104</v>
+        <v>6957739</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4130,45 +4130,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128735857</v>
+        <v>128733359</v>
       </c>
       <c r="B36" t="n">
-        <v>80257</v>
+        <v>57876</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569825</v>
+        <v>569926</v>
       </c>
       <c r="R36" t="n">
-        <v>6957814</v>
+        <v>6958108</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4227,50 +4232,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128733359</v>
+        <v>128735857</v>
       </c>
       <c r="B37" t="n">
-        <v>57876</v>
+        <v>80257</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569926</v>
+        <v>569825</v>
       </c>
       <c r="R37" t="n">
-        <v>6958108</v>
+        <v>6957814</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128734270</v>
+        <v>128735312</v>
       </c>
       <c r="B2" t="n">
-        <v>80221</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569991</v>
+        <v>569958</v>
       </c>
       <c r="R2" t="n">
-        <v>6958010</v>
+        <v>6957882</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +750,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128735128</v>
+        <v>128734270</v>
       </c>
       <c r="B3" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569944</v>
+        <v>569991</v>
       </c>
       <c r="R3" t="n">
-        <v>6957901</v>
+        <v>6958010</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128743260</v>
+        <v>128735128</v>
       </c>
       <c r="B4" t="n">
-        <v>56898</v>
+        <v>80225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569945</v>
+        <v>569944</v>
       </c>
       <c r="R4" t="n">
-        <v>6957777</v>
+        <v>6957901</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +949,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,49 +975,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735312</v>
+        <v>128735449</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>91499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569958</v>
+        <v>570013</v>
       </c>
       <c r="R5" t="n">
-        <v>6957882</v>
+        <v>6957861</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128735449</v>
+        <v>128743260</v>
       </c>
       <c r="B6" t="n">
-        <v>91494</v>
+        <v>56898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1112,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570013</v>
+        <v>569945</v>
       </c>
       <c r="R6" t="n">
-        <v>6957861</v>
+        <v>6957777</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,6 +1143,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,7 +1177,7 @@
         <v>128735195</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128734997</v>
       </c>
       <c r="B8" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>128735507</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,32 +1692,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128735988</v>
+        <v>128734913</v>
       </c>
       <c r="B12" t="n">
-        <v>91512</v>
+        <v>80254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569802</v>
+        <v>569924</v>
       </c>
       <c r="R12" t="n">
-        <v>6957819</v>
+        <v>6957910</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128734913</v>
+        <v>128736431</v>
       </c>
       <c r="B13" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569924</v>
+        <v>569829</v>
       </c>
       <c r="R13" t="n">
-        <v>6957910</v>
+        <v>6957746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,32 +1886,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128736431</v>
+        <v>128736020</v>
       </c>
       <c r="B14" t="n">
-        <v>80250</v>
+        <v>80225</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569829</v>
+        <v>569789</v>
       </c>
       <c r="R14" t="n">
-        <v>6957746</v>
+        <v>6957820</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128736020</v>
+        <v>128735988</v>
       </c>
       <c r="B15" t="n">
-        <v>80221</v>
+        <v>91517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569789</v>
+        <v>569802</v>
       </c>
       <c r="R15" t="n">
-        <v>6957820</v>
+        <v>6957819</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2394,7 +2394,7 @@
         <v>128735623</v>
       </c>
       <c r="B19" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128733844</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>128735901</v>
       </c>
       <c r="B23" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128733608</v>
+        <v>128735718</v>
       </c>
       <c r="B24" t="n">
         <v>57716</v>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569939</v>
+        <v>569857</v>
       </c>
       <c r="R24" t="n">
-        <v>6958006</v>
+        <v>6957746</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128735718</v>
+        <v>128733608</v>
       </c>
       <c r="B25" t="n">
         <v>57716</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569857</v>
+        <v>569939</v>
       </c>
       <c r="R25" t="n">
-        <v>6957746</v>
+        <v>6958006</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3131,7 +3131,7 @@
         <v>128733310</v>
       </c>
       <c r="B26" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,45 +3229,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128743251</v>
+        <v>128733449</v>
       </c>
       <c r="B27" t="n">
-        <v>97490</v>
+        <v>98625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569826</v>
+        <v>569942</v>
       </c>
       <c r="R27" t="n">
-        <v>6957739</v>
+        <v>6958086</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,49 +3330,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128733449</v>
+        <v>128743251</v>
       </c>
       <c r="B28" t="n">
-        <v>98619</v>
+        <v>97496</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569942</v>
+        <v>569826</v>
       </c>
       <c r="R28" t="n">
-        <v>6958086</v>
+        <v>6957739</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
         <v>128733496</v>
       </c>
       <c r="B29" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128737501</v>
+        <v>128735659</v>
       </c>
       <c r="B30" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,21 +3539,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569789</v>
+        <v>570026</v>
       </c>
       <c r="R30" t="n">
-        <v>6957820</v>
+        <v>6957897</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128735659</v>
+        <v>128737501</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>91517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>570026</v>
+        <v>569789</v>
       </c>
       <c r="R31" t="n">
-        <v>6957897</v>
+        <v>6957820</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3832,7 +3832,7 @@
         <v>128736806</v>
       </c>
       <c r="B33" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>128734237</v>
       </c>
       <c r="B35" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4130,50 +4130,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128733359</v>
+        <v>128735857</v>
       </c>
       <c r="B36" t="n">
-        <v>57876</v>
+        <v>80261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569926</v>
+        <v>569825</v>
       </c>
       <c r="R36" t="n">
-        <v>6958108</v>
+        <v>6957814</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,45 +4227,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128735857</v>
+        <v>128733359</v>
       </c>
       <c r="B37" t="n">
-        <v>80257</v>
+        <v>57876</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569825</v>
+        <v>569926</v>
       </c>
       <c r="R37" t="n">
-        <v>6957814</v>
+        <v>6958108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,38 +4329,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128737787</v>
+        <v>128734316</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>98625</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4369,10 +4368,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569763</v>
+        <v>569991</v>
       </c>
       <c r="R38" t="n">
-        <v>6957837</v>
+        <v>6958010</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4409,7 +4408,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4439,7 +4438,7 @@
         <v>128735254</v>
       </c>
       <c r="B39" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4536,7 +4535,7 @@
         <v>128735869</v>
       </c>
       <c r="B40" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4630,37 +4629,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128734316</v>
+        <v>128737787</v>
       </c>
       <c r="B41" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569991</v>
+        <v>569763</v>
       </c>
       <c r="R41" t="n">
-        <v>6958010</v>
+        <v>6957837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4739,7 +4739,7 @@
         <v>128733519</v>
       </c>
       <c r="B42" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>128743259</v>
       </c>
       <c r="B43" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128735020</v>
       </c>
       <c r="B44" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>128737653</v>
       </c>
       <c r="B45" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5138,45 +5138,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128743258</v>
+        <v>128735159</v>
       </c>
       <c r="B46" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569769</v>
+        <v>569925</v>
       </c>
       <c r="R46" t="n">
-        <v>6957830</v>
+        <v>6957856</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5213,7 +5218,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5240,50 +5245,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128735159</v>
+        <v>128743258</v>
       </c>
       <c r="B47" t="n">
-        <v>57716</v>
+        <v>98625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569925</v>
+        <v>569769</v>
       </c>
       <c r="R47" t="n">
-        <v>6957856</v>
+        <v>6957830</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128735312</v>
+        <v>128743260</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>56898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569958</v>
+        <v>569945</v>
       </c>
       <c r="R2" t="n">
-        <v>6957882</v>
+        <v>6957777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ett exemplar har blommat</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128734270</v>
+        <v>128735449</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569991</v>
+        <v>570013</v>
       </c>
       <c r="R3" t="n">
-        <v>6958010</v>
+        <v>6957861</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128735128</v>
+        <v>128734270</v>
       </c>
       <c r="B4" t="n">
         <v>80225</v>
@@ -913,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569944</v>
+        <v>569991</v>
       </c>
       <c r="R4" t="n">
-        <v>6957901</v>
+        <v>6958010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735449</v>
+        <v>128735128</v>
       </c>
       <c r="B5" t="n">
-        <v>91499</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570013</v>
+        <v>569944</v>
       </c>
       <c r="R5" t="n">
-        <v>6957861</v>
+        <v>6957901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128743260</v>
+        <v>128735312</v>
       </c>
       <c r="B6" t="n">
-        <v>56898</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569945</v>
+        <v>569958</v>
       </c>
       <c r="R6" t="n">
-        <v>6957777</v>
+        <v>6957882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,7 +1177,7 @@
         <v>128735195</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>128735507</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,32 +1692,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128734913</v>
+        <v>128735988</v>
       </c>
       <c r="B12" t="n">
-        <v>80254</v>
+        <v>91522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569924</v>
+        <v>569802</v>
       </c>
       <c r="R12" t="n">
-        <v>6957910</v>
+        <v>6957819</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128736431</v>
+        <v>128734913</v>
       </c>
       <c r="B13" t="n">
         <v>80254</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569829</v>
+        <v>569924</v>
       </c>
       <c r="R13" t="n">
-        <v>6957746</v>
+        <v>6957910</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,32 +1886,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128736020</v>
+        <v>128736431</v>
       </c>
       <c r="B14" t="n">
-        <v>80225</v>
+        <v>80254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569789</v>
+        <v>569829</v>
       </c>
       <c r="R14" t="n">
-        <v>6957820</v>
+        <v>6957746</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128735988</v>
+        <v>128736020</v>
       </c>
       <c r="B15" t="n">
-        <v>91517</v>
+        <v>80225</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569802</v>
+        <v>569789</v>
       </c>
       <c r="R15" t="n">
-        <v>6957819</v>
+        <v>6957820</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2394,7 +2394,7 @@
         <v>128735623</v>
       </c>
       <c r="B19" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128733844</v>
       </c>
       <c r="B22" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>128735901</v>
       </c>
       <c r="B23" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,50 +2914,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128735718</v>
+        <v>128743251</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>97503</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569857</v>
+        <v>569826</v>
       </c>
       <c r="R24" t="n">
-        <v>6957746</v>
+        <v>6957739</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,11 +2985,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3021,38 +3011,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128733608</v>
+        <v>128733310</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3061,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569939</v>
+        <v>569917</v>
       </c>
       <c r="R25" t="n">
-        <v>6958006</v>
+        <v>6958104</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3097,11 +3086,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3128,10 +3112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128733310</v>
+        <v>128733449</v>
       </c>
       <c r="B26" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3158,7 +3142,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3167,10 +3151,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569917</v>
+        <v>569942</v>
       </c>
       <c r="R26" t="n">
-        <v>6958104</v>
+        <v>6958086</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3229,37 +3213,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128733449</v>
+        <v>128735718</v>
       </c>
       <c r="B27" t="n">
-        <v>98625</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3268,10 +3253,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569942</v>
+        <v>569857</v>
       </c>
       <c r="R27" t="n">
-        <v>6958086</v>
+        <v>6957746</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3304,6 +3289,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3330,45 +3320,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128743251</v>
+        <v>128733608</v>
       </c>
       <c r="B28" t="n">
-        <v>97496</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569826</v>
+        <v>569939</v>
       </c>
       <c r="R28" t="n">
-        <v>6957739</v>
+        <v>6958006</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3401,6 +3396,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3430,7 +3430,7 @@
         <v>128733496</v>
       </c>
       <c r="B29" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128735659</v>
+        <v>128737501</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,21 +3539,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570026</v>
+        <v>569789</v>
       </c>
       <c r="R30" t="n">
-        <v>6957897</v>
+        <v>6957820</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128737501</v>
+        <v>128735659</v>
       </c>
       <c r="B31" t="n">
-        <v>91517</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569789</v>
+        <v>570026</v>
       </c>
       <c r="R31" t="n">
-        <v>6957820</v>
+        <v>6957897</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3832,7 +3832,7 @@
         <v>128736806</v>
       </c>
       <c r="B33" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>128734237</v>
       </c>
       <c r="B35" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4130,45 +4130,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128735857</v>
+        <v>128733359</v>
       </c>
       <c r="B36" t="n">
-        <v>80261</v>
+        <v>57876</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569825</v>
+        <v>569926</v>
       </c>
       <c r="R36" t="n">
-        <v>6957814</v>
+        <v>6958108</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4227,50 +4232,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128733359</v>
+        <v>128735857</v>
       </c>
       <c r="B37" t="n">
-        <v>57876</v>
+        <v>80261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569926</v>
+        <v>569825</v>
       </c>
       <c r="R37" t="n">
-        <v>6958108</v>
+        <v>6957814</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,37 +4329,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128734316</v>
+        <v>128737787</v>
       </c>
       <c r="B38" t="n">
-        <v>98625</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4368,10 +4369,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569991</v>
+        <v>569763</v>
       </c>
       <c r="R38" t="n">
-        <v>6958010</v>
+        <v>6957837</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4408,7 +4409,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4435,45 +4436,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128735254</v>
+        <v>128734316</v>
       </c>
       <c r="B39" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569890</v>
+        <v>569991</v>
       </c>
       <c r="R39" t="n">
-        <v>6957854</v>
+        <v>6958010</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4506,6 +4511,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4532,7 +4542,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128735869</v>
+        <v>128735254</v>
       </c>
       <c r="B40" t="n">
         <v>80225</v>
@@ -4567,10 +4577,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569825</v>
+        <v>569890</v>
       </c>
       <c r="R40" t="n">
-        <v>6957814</v>
+        <v>6957854</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4629,10 +4639,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128737787</v>
+        <v>128735869</v>
       </c>
       <c r="B41" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4640,39 +4650,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569763</v>
+        <v>569825</v>
       </c>
       <c r="R41" t="n">
-        <v>6957837</v>
+        <v>6957814</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4705,11 +4710,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4739,7 +4739,7 @@
         <v>128733519</v>
       </c>
       <c r="B42" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>128743259</v>
       </c>
       <c r="B43" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>128743258</v>
       </c>
       <c r="B47" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128743260</v>
+        <v>128735449</v>
       </c>
       <c r="B2" t="n">
-        <v>56898</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569945</v>
+        <v>570013</v>
       </c>
       <c r="R2" t="n">
-        <v>6957777</v>
+        <v>6957861</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128735449</v>
+        <v>128743260</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>56898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570013</v>
+        <v>569945</v>
       </c>
       <c r="R3" t="n">
-        <v>6957861</v>
+        <v>6957777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1692,32 +1692,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128735988</v>
+        <v>128734913</v>
       </c>
       <c r="B12" t="n">
-        <v>91522</v>
+        <v>80254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569802</v>
+        <v>569924</v>
       </c>
       <c r="R12" t="n">
-        <v>6957819</v>
+        <v>6957910</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128734913</v>
+        <v>128736431</v>
       </c>
       <c r="B13" t="n">
         <v>80254</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569924</v>
+        <v>569829</v>
       </c>
       <c r="R13" t="n">
-        <v>6957910</v>
+        <v>6957746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,32 +1886,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128736431</v>
+        <v>128736020</v>
       </c>
       <c r="B14" t="n">
-        <v>80254</v>
+        <v>80225</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569829</v>
+        <v>569789</v>
       </c>
       <c r="R14" t="n">
-        <v>6957746</v>
+        <v>6957820</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128736020</v>
+        <v>128735988</v>
       </c>
       <c r="B15" t="n">
-        <v>80225</v>
+        <v>91522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569789</v>
+        <v>569802</v>
       </c>
       <c r="R15" t="n">
-        <v>6957820</v>
+        <v>6957819</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2817,45 +2817,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128735901</v>
+        <v>128733608</v>
       </c>
       <c r="B23" t="n">
-        <v>91469</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569825</v>
+        <v>569939</v>
       </c>
       <c r="R23" t="n">
-        <v>6957814</v>
+        <v>6958006</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2888,6 +2893,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3011,49 +3021,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128733310</v>
+        <v>128735901</v>
       </c>
       <c r="B25" t="n">
-        <v>98632</v>
+        <v>91469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569917</v>
+        <v>569825</v>
       </c>
       <c r="R25" t="n">
-        <v>6958104</v>
+        <v>6957814</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3112,37 +3118,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128733449</v>
+        <v>128735718</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3151,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569942</v>
+        <v>569857</v>
       </c>
       <c r="R26" t="n">
-        <v>6958086</v>
+        <v>6957746</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3187,6 +3194,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3213,38 +3225,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128735718</v>
+        <v>128733310</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3253,10 +3264,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569857</v>
+        <v>569917</v>
       </c>
       <c r="R27" t="n">
-        <v>6957746</v>
+        <v>6958104</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3289,11 +3300,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3320,38 +3326,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128733608</v>
+        <v>128733449</v>
       </c>
       <c r="B28" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3360,10 +3365,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569939</v>
+        <v>569942</v>
       </c>
       <c r="R28" t="n">
-        <v>6958006</v>
+        <v>6958086</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3396,11 +3401,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3528,10 +3528,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128737501</v>
+        <v>128735659</v>
       </c>
       <c r="B30" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,21 +3539,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569789</v>
+        <v>570026</v>
       </c>
       <c r="R30" t="n">
-        <v>6957820</v>
+        <v>6957897</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128735659</v>
+        <v>128737501</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>570026</v>
+        <v>569789</v>
       </c>
       <c r="R31" t="n">
-        <v>6957897</v>
+        <v>6957820</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3829,10 +3829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128736806</v>
+        <v>128735365</v>
       </c>
       <c r="B33" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,34 +3840,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569928</v>
+        <v>569970</v>
       </c>
       <c r="R33" t="n">
-        <v>6957738</v>
+        <v>6957886</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3900,6 +3905,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3926,10 +3936,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128735365</v>
+        <v>128736806</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,39 +3947,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569970</v>
+        <v>569928</v>
       </c>
       <c r="R34" t="n">
-        <v>6957886</v>
+        <v>6957738</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4002,11 +4007,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4130,50 +4130,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128733359</v>
+        <v>128735857</v>
       </c>
       <c r="B36" t="n">
-        <v>57876</v>
+        <v>80261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569926</v>
+        <v>569825</v>
       </c>
       <c r="R36" t="n">
-        <v>6958108</v>
+        <v>6957814</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,45 +4227,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128735857</v>
+        <v>128733359</v>
       </c>
       <c r="B37" t="n">
-        <v>80261</v>
+        <v>57876</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569825</v>
+        <v>569926</v>
       </c>
       <c r="R37" t="n">
-        <v>6957814</v>
+        <v>6958108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,10 +4329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128737787</v>
+        <v>128735254</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,39 +4340,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569763</v>
+        <v>569890</v>
       </c>
       <c r="R38" t="n">
-        <v>6957837</v>
+        <v>6957854</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4405,11 +4400,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4436,49 +4426,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128734316</v>
+        <v>128735869</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569991</v>
+        <v>569825</v>
       </c>
       <c r="R39" t="n">
-        <v>6958010</v>
+        <v>6957814</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4511,11 +4497,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4542,10 +4523,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128735254</v>
+        <v>128737787</v>
       </c>
       <c r="B40" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,34 +4534,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569890</v>
+        <v>569763</v>
       </c>
       <c r="R40" t="n">
-        <v>6957854</v>
+        <v>6957837</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4613,6 +4599,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4639,45 +4630,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128735869</v>
+        <v>128734316</v>
       </c>
       <c r="B41" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569825</v>
+        <v>569991</v>
       </c>
       <c r="R41" t="n">
-        <v>6957814</v>
+        <v>6958010</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4710,6 +4705,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128735449</v>
+        <v>128743260</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>56898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570013</v>
+        <v>569945</v>
       </c>
       <c r="R2" t="n">
-        <v>6957861</v>
+        <v>6957777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,45 +777,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128743260</v>
+        <v>128735312</v>
       </c>
       <c r="B3" t="n">
-        <v>56898</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569945</v>
+        <v>569958</v>
       </c>
       <c r="R3" t="n">
-        <v>6957777</v>
+        <v>6957882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +856,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128734270</v>
+        <v>128735449</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569991</v>
+        <v>570013</v>
       </c>
       <c r="R4" t="n">
-        <v>6958010</v>
+        <v>6957861</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +980,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735128</v>
+        <v>128734270</v>
       </c>
       <c r="B5" t="n">
         <v>80225</v>
@@ -1006,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569944</v>
+        <v>569991</v>
       </c>
       <c r="R5" t="n">
-        <v>6957901</v>
+        <v>6958010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,49 +1077,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128735312</v>
+        <v>128735128</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569958</v>
+        <v>569944</v>
       </c>
       <c r="R6" t="n">
-        <v>6957882</v>
+        <v>6957901</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,11 +1148,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1692,32 +1692,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128734913</v>
+        <v>128735988</v>
       </c>
       <c r="B12" t="n">
-        <v>80254</v>
+        <v>91522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569924</v>
+        <v>569802</v>
       </c>
       <c r="R12" t="n">
-        <v>6957910</v>
+        <v>6957819</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128736431</v>
+        <v>128734913</v>
       </c>
       <c r="B13" t="n">
         <v>80254</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569829</v>
+        <v>569924</v>
       </c>
       <c r="R13" t="n">
-        <v>6957746</v>
+        <v>6957910</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,32 +1886,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128736020</v>
+        <v>128736431</v>
       </c>
       <c r="B14" t="n">
-        <v>80225</v>
+        <v>80254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569789</v>
+        <v>569829</v>
       </c>
       <c r="R14" t="n">
-        <v>6957820</v>
+        <v>6957746</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128735988</v>
+        <v>128736020</v>
       </c>
       <c r="B15" t="n">
-        <v>91522</v>
+        <v>80225</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569802</v>
+        <v>569789</v>
       </c>
       <c r="R15" t="n">
-        <v>6957819</v>
+        <v>6957820</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743248</v>
+        <v>128743249</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569853</v>
+        <v>569769</v>
       </c>
       <c r="R16" t="n">
-        <v>6957734</v>
+        <v>6957830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,7 +2182,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128736601</v>
+        <v>128743248</v>
       </c>
       <c r="B17" t="n">
         <v>57716</v>
@@ -2211,21 +2211,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569845</v>
+        <v>569853</v>
       </c>
       <c r="R17" t="n">
-        <v>6957673</v>
+        <v>6957734</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2257,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2289,10 +2284,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128743249</v>
+        <v>128736601</v>
       </c>
       <c r="B18" t="n">
-        <v>57876</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,34 +2295,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569769</v>
+        <v>569845</v>
       </c>
       <c r="R18" t="n">
-        <v>6957830</v>
+        <v>6957673</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2817,50 +2817,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128733608</v>
+        <v>128743251</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>97503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569939</v>
+        <v>569826</v>
       </c>
       <c r="R23" t="n">
-        <v>6958006</v>
+        <v>6957739</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,11 +2888,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2924,10 +2914,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128743251</v>
+        <v>128735901</v>
       </c>
       <c r="B24" t="n">
-        <v>97503</v>
+        <v>91469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2935,21 +2925,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2949,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569826</v>
+        <v>569825</v>
       </c>
       <c r="R24" t="n">
-        <v>6957739</v>
+        <v>6957814</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,45 +3011,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128735901</v>
+        <v>128735718</v>
       </c>
       <c r="B25" t="n">
-        <v>91469</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569825</v>
+        <v>569857</v>
       </c>
       <c r="R25" t="n">
-        <v>6957814</v>
+        <v>6957746</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3092,6 +3087,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3118,7 +3118,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128735718</v>
+        <v>128733608</v>
       </c>
       <c r="B26" t="n">
         <v>57716</v>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569857</v>
+        <v>569939</v>
       </c>
       <c r="R26" t="n">
-        <v>6957746</v>
+        <v>6958006</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128735659</v>
+        <v>128737501</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,21 +3539,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570026</v>
+        <v>569789</v>
       </c>
       <c r="R30" t="n">
-        <v>6957897</v>
+        <v>6957820</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128737501</v>
+        <v>128735659</v>
       </c>
       <c r="B31" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569789</v>
+        <v>570026</v>
       </c>
       <c r="R31" t="n">
-        <v>6957820</v>
+        <v>6957897</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3829,10 +3829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128735365</v>
+        <v>128736806</v>
       </c>
       <c r="B33" t="n">
-        <v>57716</v>
+        <v>91522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,39 +3840,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569970</v>
+        <v>569928</v>
       </c>
       <c r="R33" t="n">
-        <v>6957886</v>
+        <v>6957738</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3905,11 +3900,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,10 +3926,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128736806</v>
+        <v>128735365</v>
       </c>
       <c r="B34" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,34 +3937,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569928</v>
+        <v>569970</v>
       </c>
       <c r="R34" t="n">
-        <v>6957738</v>
+        <v>6957886</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4007,6 +4002,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4130,45 +4130,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128735857</v>
+        <v>128733359</v>
       </c>
       <c r="B36" t="n">
-        <v>80261</v>
+        <v>57876</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569825</v>
+        <v>569926</v>
       </c>
       <c r="R36" t="n">
-        <v>6957814</v>
+        <v>6958108</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4227,50 +4232,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128733359</v>
+        <v>128735857</v>
       </c>
       <c r="B37" t="n">
-        <v>57876</v>
+        <v>80261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569926</v>
+        <v>569825</v>
       </c>
       <c r="R37" t="n">
-        <v>6958108</v>
+        <v>6957814</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128743260</v>
+        <v>128735449</v>
       </c>
       <c r="B2" t="n">
-        <v>56898</v>
+        <v>91508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569945</v>
+        <v>570013</v>
       </c>
       <c r="R2" t="n">
-        <v>6957777</v>
+        <v>6957861</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128735312</v>
+        <v>128743260</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>56901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569958</v>
+        <v>569945</v>
       </c>
       <c r="R3" t="n">
-        <v>6957882</v>
+        <v>6957777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ett exemplar har blommat</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128735449</v>
+        <v>128734270</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>80229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570013</v>
+        <v>569991</v>
       </c>
       <c r="R4" t="n">
-        <v>6957861</v>
+        <v>6958010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128734270</v>
+        <v>128735128</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569991</v>
+        <v>569944</v>
       </c>
       <c r="R5" t="n">
-        <v>6958010</v>
+        <v>6957901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128735128</v>
+        <v>128735312</v>
       </c>
       <c r="B6" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569944</v>
+        <v>569958</v>
       </c>
       <c r="R6" t="n">
-        <v>6957901</v>
+        <v>6957882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,6 +1143,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,7 +1177,7 @@
         <v>128735195</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128734997</v>
       </c>
       <c r="B8" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128735394</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>128735512</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>128735507</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,32 +1692,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128735988</v>
+        <v>128734913</v>
       </c>
       <c r="B12" t="n">
-        <v>91522</v>
+        <v>80258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569802</v>
+        <v>569924</v>
       </c>
       <c r="R12" t="n">
-        <v>6957819</v>
+        <v>6957910</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128734913</v>
+        <v>128736431</v>
       </c>
       <c r="B13" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569924</v>
+        <v>569829</v>
       </c>
       <c r="R13" t="n">
-        <v>6957910</v>
+        <v>6957746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,32 +1886,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128736431</v>
+        <v>128736020</v>
       </c>
       <c r="B14" t="n">
-        <v>80254</v>
+        <v>80229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569829</v>
+        <v>569789</v>
       </c>
       <c r="R14" t="n">
-        <v>6957746</v>
+        <v>6957820</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128736020</v>
+        <v>128735988</v>
       </c>
       <c r="B15" t="n">
-        <v>80225</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569789</v>
+        <v>569802</v>
       </c>
       <c r="R15" t="n">
-        <v>6957820</v>
+        <v>6957819</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743249</v>
+        <v>128743248</v>
       </c>
       <c r="B16" t="n">
-        <v>57876</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569769</v>
+        <v>569853</v>
       </c>
       <c r="R16" t="n">
-        <v>6957830</v>
+        <v>6957734</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,10 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128743248</v>
+        <v>128736601</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,16 +2211,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569853</v>
+        <v>569845</v>
       </c>
       <c r="R17" t="n">
-        <v>6957734</v>
+        <v>6957673</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,7 +2262,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2284,10 +2289,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128736601</v>
+        <v>128743249</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>57880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2295,39 +2300,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569845</v>
+        <v>569769</v>
       </c>
       <c r="R18" t="n">
-        <v>6957673</v>
+        <v>6957830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,7 +2394,7 @@
         <v>128735623</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>128735562</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>128734344</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128733844</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,45 +2817,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128743251</v>
+        <v>128735718</v>
       </c>
       <c r="B23" t="n">
-        <v>97503</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569826</v>
+        <v>569857</v>
       </c>
       <c r="R23" t="n">
-        <v>6957739</v>
+        <v>6957746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2888,6 +2893,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2914,45 +2924,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128735901</v>
+        <v>128733608</v>
       </c>
       <c r="B24" t="n">
-        <v>91469</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569825</v>
+        <v>569939</v>
       </c>
       <c r="R24" t="n">
-        <v>6957814</v>
+        <v>6958006</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2985,6 +3000,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3011,50 +3031,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128735718</v>
+        <v>128743251</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>97507</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569857</v>
+        <v>569826</v>
       </c>
       <c r="R25" t="n">
-        <v>6957746</v>
+        <v>6957739</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,11 +3102,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3118,50 +3128,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128733608</v>
+        <v>128735901</v>
       </c>
       <c r="B26" t="n">
-        <v>57716</v>
+        <v>91473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569939</v>
+        <v>569825</v>
       </c>
       <c r="R26" t="n">
-        <v>6958006</v>
+        <v>6957814</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3194,11 +3199,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3228,7 +3228,7 @@
         <v>128733310</v>
       </c>
       <c r="B27" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128733449</v>
       </c>
       <c r="B28" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128733496</v>
       </c>
       <c r="B29" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>128737501</v>
       </c>
       <c r="B30" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>128735659</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>128734061</v>
       </c>
       <c r="B32" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3829,10 +3829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128736806</v>
+        <v>128735365</v>
       </c>
       <c r="B33" t="n">
-        <v>91522</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,34 +3840,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569928</v>
+        <v>569970</v>
       </c>
       <c r="R33" t="n">
-        <v>6957738</v>
+        <v>6957886</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3900,6 +3905,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3926,10 +3936,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128735365</v>
+        <v>128736806</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>91526</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,39 +3947,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569970</v>
+        <v>569928</v>
       </c>
       <c r="R34" t="n">
-        <v>6957886</v>
+        <v>6957738</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4002,11 +4007,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4036,7 +4036,7 @@
         <v>128734237</v>
       </c>
       <c r="B35" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4130,50 +4130,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128733359</v>
+        <v>128735857</v>
       </c>
       <c r="B36" t="n">
-        <v>57876</v>
+        <v>80265</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569926</v>
+        <v>569825</v>
       </c>
       <c r="R36" t="n">
-        <v>6958108</v>
+        <v>6957814</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,45 +4227,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128735857</v>
+        <v>128733359</v>
       </c>
       <c r="B37" t="n">
-        <v>80261</v>
+        <v>57880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569825</v>
+        <v>569926</v>
       </c>
       <c r="R37" t="n">
-        <v>6957814</v>
+        <v>6958108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4332,7 +4332,7 @@
         <v>128735254</v>
       </c>
       <c r="B38" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>128735869</v>
       </c>
       <c r="B39" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>128737787</v>
       </c>
       <c r="B40" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>128734316</v>
       </c>
       <c r="B41" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>128733519</v>
       </c>
       <c r="B42" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>128743259</v>
       </c>
       <c r="B43" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128735020</v>
       </c>
       <c r="B44" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>128737653</v>
       </c>
       <c r="B45" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>128735159</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>128743258</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>128736388</v>
       </c>
       <c r="B48" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>128733395</v>
       </c>
       <c r="B49" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128735449</v>
+        <v>128734270</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>80229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570013</v>
+        <v>569991</v>
       </c>
       <c r="R2" t="n">
-        <v>6957861</v>
+        <v>6958010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128743260</v>
+        <v>128735128</v>
       </c>
       <c r="B3" t="n">
-        <v>56901</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569945</v>
+        <v>569944</v>
       </c>
       <c r="R3" t="n">
-        <v>6957777</v>
+        <v>6957901</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128734270</v>
+        <v>128735449</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>91508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569991</v>
+        <v>570013</v>
       </c>
       <c r="R4" t="n">
-        <v>6958010</v>
+        <v>6957861</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735128</v>
+        <v>128743260</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>56901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569944</v>
+        <v>569945</v>
       </c>
       <c r="R5" t="n">
-        <v>6957901</v>
+        <v>6957777</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743248</v>
+        <v>128743249</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569853</v>
+        <v>569769</v>
       </c>
       <c r="R16" t="n">
-        <v>6957734</v>
+        <v>6957830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,7 +2182,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128736601</v>
+        <v>128743248</v>
       </c>
       <c r="B17" t="n">
         <v>57720</v>
@@ -2211,21 +2211,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569845</v>
+        <v>569853</v>
       </c>
       <c r="R17" t="n">
-        <v>6957673</v>
+        <v>6957734</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2257,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2289,10 +2284,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128743249</v>
+        <v>128736601</v>
       </c>
       <c r="B18" t="n">
-        <v>57880</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,34 +2295,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569769</v>
+        <v>569845</v>
       </c>
       <c r="R18" t="n">
-        <v>6957830</v>
+        <v>6957673</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,38 +2497,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128735562</v>
+        <v>128733844</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2537,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569865</v>
+        <v>569954</v>
       </c>
       <c r="R20" t="n">
-        <v>6957790</v>
+        <v>6958059</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,7 +2576,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 exemplar har blommat</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2604,7 +2603,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128734344</v>
+        <v>128735562</v>
       </c>
       <c r="B21" t="n">
         <v>57720</v>
@@ -2635,7 +2634,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2644,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570110</v>
+        <v>569865</v>
       </c>
       <c r="R21" t="n">
-        <v>6958034</v>
+        <v>6957790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,37 +2710,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128733844</v>
+        <v>128734344</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569954</v>
+        <v>570110</v>
       </c>
       <c r="R22" t="n">
-        <v>6958059</v>
+        <v>6958034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 exemplar har blommat</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128743251</v>
+        <v>128735901</v>
       </c>
       <c r="B25" t="n">
-        <v>97507</v>
+        <v>91473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569826</v>
+        <v>569825</v>
       </c>
       <c r="R25" t="n">
-        <v>6957739</v>
+        <v>6957814</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,45 +3128,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128735901</v>
+        <v>128733310</v>
       </c>
       <c r="B26" t="n">
-        <v>91473</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569825</v>
+        <v>569917</v>
       </c>
       <c r="R26" t="n">
-        <v>6957814</v>
+        <v>6958104</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,7 +3229,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128733310</v>
+        <v>128733449</v>
       </c>
       <c r="B27" t="n">
         <v>98636</v>
@@ -3255,7 +3259,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3264,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569917</v>
+        <v>569942</v>
       </c>
       <c r="R27" t="n">
-        <v>6958104</v>
+        <v>6958086</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,49 +3330,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128733449</v>
+        <v>128743251</v>
       </c>
       <c r="B28" t="n">
-        <v>98636</v>
+        <v>97507</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569942</v>
+        <v>569826</v>
       </c>
       <c r="R28" t="n">
-        <v>6958086</v>
+        <v>6957739</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3829,10 +3829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128735365</v>
+        <v>128736806</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>91526</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,39 +3840,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569970</v>
+        <v>569928</v>
       </c>
       <c r="R33" t="n">
-        <v>6957886</v>
+        <v>6957738</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3905,11 +3900,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,10 +3926,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128736806</v>
+        <v>128735365</v>
       </c>
       <c r="B34" t="n">
-        <v>91526</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,34 +3937,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569928</v>
+        <v>569970</v>
       </c>
       <c r="R34" t="n">
-        <v>6957738</v>
+        <v>6957886</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4007,6 +4002,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128735449</v>
+        <v>128743260</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>56901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570013</v>
+        <v>569945</v>
       </c>
       <c r="R4" t="n">
-        <v>6957861</v>
+        <v>6957777</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,45 +971,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128743260</v>
+        <v>128735312</v>
       </c>
       <c r="B5" t="n">
-        <v>56901</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569945</v>
+        <v>569958</v>
       </c>
       <c r="R5" t="n">
-        <v>6957777</v>
+        <v>6957882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,7 +1050,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,49 +1077,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128735312</v>
+        <v>128735449</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>91508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569958</v>
+        <v>570013</v>
       </c>
       <c r="R6" t="n">
-        <v>6957882</v>
+        <v>6957861</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,11 +1148,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1692,32 +1692,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128734913</v>
+        <v>128735988</v>
       </c>
       <c r="B12" t="n">
-        <v>80258</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569924</v>
+        <v>569802</v>
       </c>
       <c r="R12" t="n">
-        <v>6957910</v>
+        <v>6957819</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128736431</v>
+        <v>128734913</v>
       </c>
       <c r="B13" t="n">
         <v>80258</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569829</v>
+        <v>569924</v>
       </c>
       <c r="R13" t="n">
-        <v>6957746</v>
+        <v>6957910</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,32 +1886,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128736020</v>
+        <v>128736431</v>
       </c>
       <c r="B14" t="n">
-        <v>80229</v>
+        <v>80258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569789</v>
+        <v>569829</v>
       </c>
       <c r="R14" t="n">
-        <v>6957820</v>
+        <v>6957746</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128735988</v>
+        <v>128736020</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>80229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569802</v>
+        <v>569789</v>
       </c>
       <c r="R15" t="n">
-        <v>6957819</v>
+        <v>6957820</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743249</v>
+        <v>128743248</v>
       </c>
       <c r="B16" t="n">
-        <v>57880</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569769</v>
+        <v>569853</v>
       </c>
       <c r="R16" t="n">
-        <v>6957830</v>
+        <v>6957734</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,7 +2182,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128743248</v>
+        <v>128736601</v>
       </c>
       <c r="B17" t="n">
         <v>57720</v>
@@ -2211,16 +2211,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569853</v>
+        <v>569845</v>
       </c>
       <c r="R17" t="n">
-        <v>6957734</v>
+        <v>6957673</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,7 +2262,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2284,10 +2289,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128736601</v>
+        <v>128743249</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2295,39 +2300,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569845</v>
+        <v>569769</v>
       </c>
       <c r="R18" t="n">
-        <v>6957673</v>
+        <v>6957830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,37 +2497,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128733844</v>
+        <v>128735562</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2536,10 +2537,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569954</v>
+        <v>569865</v>
       </c>
       <c r="R20" t="n">
-        <v>6958059</v>
+        <v>6957790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2577,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 exemplar har blommat</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2603,7 +2604,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128735562</v>
+        <v>128734344</v>
       </c>
       <c r="B21" t="n">
         <v>57720</v>
@@ -2634,7 +2635,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2643,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569865</v>
+        <v>570110</v>
       </c>
       <c r="R21" t="n">
-        <v>6957790</v>
+        <v>6958034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,38 +2711,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128734344</v>
+        <v>128733844</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570110</v>
+        <v>569954</v>
       </c>
       <c r="R22" t="n">
-        <v>6958034</v>
+        <v>6958059</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 exemplar har blommat</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3229,49 +3229,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128733449</v>
+        <v>128743251</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>97507</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569942</v>
+        <v>569826</v>
       </c>
       <c r="R27" t="n">
-        <v>6958086</v>
+        <v>6957739</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3330,45 +3326,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128743251</v>
+        <v>128733449</v>
       </c>
       <c r="B28" t="n">
-        <v>97507</v>
+        <v>98636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569826</v>
+        <v>569942</v>
       </c>
       <c r="R28" t="n">
-        <v>6957739</v>
+        <v>6958086</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3829,10 +3829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128736806</v>
+        <v>128735365</v>
       </c>
       <c r="B33" t="n">
-        <v>91526</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,34 +3840,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569928</v>
+        <v>569970</v>
       </c>
       <c r="R33" t="n">
-        <v>6957738</v>
+        <v>6957886</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3900,6 +3905,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3926,10 +3936,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128735365</v>
+        <v>128736806</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>91526</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,39 +3947,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569970</v>
+        <v>569928</v>
       </c>
       <c r="R34" t="n">
-        <v>6957886</v>
+        <v>6957738</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4002,11 +4007,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4329,10 +4329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128735254</v>
+        <v>128737787</v>
       </c>
       <c r="B38" t="n">
-        <v>80229</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,34 +4340,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569890</v>
+        <v>569763</v>
       </c>
       <c r="R38" t="n">
-        <v>6957854</v>
+        <v>6957837</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,6 +4405,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4426,45 +4436,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128735869</v>
+        <v>128734316</v>
       </c>
       <c r="B39" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569825</v>
+        <v>569991</v>
       </c>
       <c r="R39" t="n">
-        <v>6957814</v>
+        <v>6958010</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4497,6 +4511,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4523,10 +4542,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128737787</v>
+        <v>128735869</v>
       </c>
       <c r="B40" t="n">
-        <v>57720</v>
+        <v>80229</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4534,39 +4553,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569763</v>
+        <v>569825</v>
       </c>
       <c r="R40" t="n">
-        <v>6957837</v>
+        <v>6957814</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4599,11 +4613,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4630,49 +4639,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128734316</v>
+        <v>128735254</v>
       </c>
       <c r="B41" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569991</v>
+        <v>569890</v>
       </c>
       <c r="R41" t="n">
-        <v>6958010</v>
+        <v>6957854</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4705,11 +4710,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734270</v>
       </c>
       <c r="B2" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128735128</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128743260</v>
+        <v>128735449</v>
       </c>
       <c r="B4" t="n">
-        <v>56901</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569945</v>
+        <v>570013</v>
       </c>
       <c r="R4" t="n">
-        <v>6957777</v>
+        <v>6957861</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,49 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735312</v>
+        <v>128743260</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>56904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569958</v>
+        <v>569945</v>
       </c>
       <c r="R5" t="n">
-        <v>6957882</v>
+        <v>6957777</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,7 +1041,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ett exemplar har blommat</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128735449</v>
+        <v>128735312</v>
       </c>
       <c r="B6" t="n">
-        <v>91508</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570013</v>
+        <v>569958</v>
       </c>
       <c r="R6" t="n">
-        <v>6957861</v>
+        <v>6957882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,6 +1143,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,7 +1177,7 @@
         <v>128735195</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128734997</v>
       </c>
       <c r="B8" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128735394</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>128735512</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>128735507</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>128735988</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>128734913</v>
       </c>
       <c r="B13" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>128736431</v>
       </c>
       <c r="B14" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128736020</v>
       </c>
       <c r="B15" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743248</v>
+        <v>128736601</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,16 +2109,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569853</v>
+        <v>569845</v>
       </c>
       <c r="R16" t="n">
-        <v>6957734</v>
+        <v>6957673</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2160,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,10 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128736601</v>
+        <v>128743249</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2193,39 +2198,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569845</v>
+        <v>569769</v>
       </c>
       <c r="R17" t="n">
-        <v>6957673</v>
+        <v>6957830</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2289,10 +2289,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128743249</v>
+        <v>128743248</v>
       </c>
       <c r="B18" t="n">
-        <v>57880</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,21 +2300,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569769</v>
+        <v>569853</v>
       </c>
       <c r="R18" t="n">
-        <v>6957830</v>
+        <v>6957734</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,7 +2394,7 @@
         <v>128735623</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>128735562</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2604,38 +2604,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128734344</v>
+        <v>128733844</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2644,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570110</v>
+        <v>569954</v>
       </c>
       <c r="R21" t="n">
-        <v>6958034</v>
+        <v>6958059</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,7 +2683,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 exemplar har blommat</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2711,37 +2710,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128733844</v>
+        <v>128734344</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569954</v>
+        <v>570110</v>
       </c>
       <c r="R22" t="n">
-        <v>6958059</v>
+        <v>6958034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 exemplar har blommat</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,50 +2817,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128735718</v>
+        <v>128735901</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>91478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569857</v>
+        <v>569825</v>
       </c>
       <c r="R23" t="n">
-        <v>6957746</v>
+        <v>6957814</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,11 +2888,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2924,10 +2914,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128733608</v>
+        <v>128735718</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2964,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569939</v>
+        <v>569857</v>
       </c>
       <c r="R24" t="n">
-        <v>6958006</v>
+        <v>6957746</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,45 +3021,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128735901</v>
+        <v>128733608</v>
       </c>
       <c r="B25" t="n">
-        <v>91473</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569825</v>
+        <v>569939</v>
       </c>
       <c r="R25" t="n">
-        <v>6957814</v>
+        <v>6958006</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3102,6 +3097,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3131,7 +3131,7 @@
         <v>128733310</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,45 +3229,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128743251</v>
+        <v>128733449</v>
       </c>
       <c r="B27" t="n">
-        <v>97507</v>
+        <v>98643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569826</v>
+        <v>569942</v>
       </c>
       <c r="R27" t="n">
-        <v>6957739</v>
+        <v>6958086</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,49 +3330,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128733449</v>
+        <v>128743251</v>
       </c>
       <c r="B28" t="n">
-        <v>98636</v>
+        <v>97514</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569942</v>
+        <v>569826</v>
       </c>
       <c r="R28" t="n">
-        <v>6958086</v>
+        <v>6957739</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
         <v>128733496</v>
       </c>
       <c r="B29" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>128737501</v>
       </c>
       <c r="B30" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128735659</v>
+        <v>128734061</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,34 +3636,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>570026</v>
+        <v>569997</v>
       </c>
       <c r="R31" t="n">
-        <v>6957897</v>
+        <v>6958070</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3696,6 +3701,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3722,10 +3732,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128734061</v>
+        <v>128735659</v>
       </c>
       <c r="B32" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3733,39 +3743,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569997</v>
+        <v>570026</v>
       </c>
       <c r="R32" t="n">
-        <v>6958070</v>
+        <v>6957897</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3798,11 +3803,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3829,10 +3829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128735365</v>
+        <v>128736806</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>91531</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,39 +3840,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569970</v>
+        <v>569928</v>
       </c>
       <c r="R33" t="n">
-        <v>6957886</v>
+        <v>6957738</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3905,11 +3900,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,10 +3926,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128736806</v>
+        <v>128735365</v>
       </c>
       <c r="B34" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,34 +3937,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569928</v>
+        <v>569970</v>
       </c>
       <c r="R34" t="n">
-        <v>6957738</v>
+        <v>6957886</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4007,6 +4002,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4036,7 +4036,7 @@
         <v>128734237</v>
       </c>
       <c r="B35" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>128735857</v>
       </c>
       <c r="B36" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>128733359</v>
       </c>
       <c r="B37" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4329,38 +4329,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128737787</v>
+        <v>128734316</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4369,10 +4368,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569763</v>
+        <v>569991</v>
       </c>
       <c r="R38" t="n">
-        <v>6957837</v>
+        <v>6958010</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4409,7 +4408,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4436,49 +4435,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128734316</v>
+        <v>128735254</v>
       </c>
       <c r="B39" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569991</v>
+        <v>569890</v>
       </c>
       <c r="R39" t="n">
-        <v>6958010</v>
+        <v>6957854</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4511,11 +4506,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4545,7 +4535,7 @@
         <v>128735869</v>
       </c>
       <c r="B40" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4639,10 +4629,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128735254</v>
+        <v>128737787</v>
       </c>
       <c r="B41" t="n">
-        <v>80229</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4650,34 +4640,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569890</v>
+        <v>569763</v>
       </c>
       <c r="R41" t="n">
-        <v>6957854</v>
+        <v>6957837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4710,6 +4705,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4736,10 +4736,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128733519</v>
+        <v>128743259</v>
       </c>
       <c r="B42" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,21 +4764,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569951</v>
+        <v>569937</v>
       </c>
       <c r="R42" t="n">
-        <v>6958068</v>
+        <v>6957753</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4815,7 +4811,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ka finnas mer I mossan</t>
+          <t>150 stycken ( ca )</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4842,10 +4838,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128743259</v>
+        <v>128733519</v>
       </c>
       <c r="B43" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,17 +4866,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569937</v>
+        <v>569951</v>
       </c>
       <c r="R43" t="n">
-        <v>6957753</v>
+        <v>6958068</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>150 stycken ( ca )</t>
+          <t>Ka finnas mer I mossan</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4947,7 +4947,7 @@
         <v>128735020</v>
       </c>
       <c r="B44" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>128737653</v>
       </c>
       <c r="B45" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>128735159</v>
       </c>
       <c r="B46" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>128743258</v>
       </c>
       <c r="B47" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>128736388</v>
       </c>
       <c r="B48" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>128733395</v>
       </c>
       <c r="B49" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128735128</v>
+        <v>128735449</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>91520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569944</v>
+        <v>570013</v>
       </c>
       <c r="R2" t="n">
-        <v>6957901</v>
+        <v>6957861</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128734270</v>
+        <v>128735128</v>
       </c>
       <c r="B3" t="n">
         <v>80139</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569991</v>
+        <v>569944</v>
       </c>
       <c r="R3" t="n">
-        <v>6958010</v>
+        <v>6957901</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128743260</v>
+        <v>128734270</v>
       </c>
       <c r="B4" t="n">
-        <v>56904</v>
+        <v>80139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569945</v>
+        <v>569991</v>
       </c>
       <c r="R4" t="n">
-        <v>6957777</v>
+        <v>6958010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,49 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735312</v>
+        <v>128743260</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>56904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569958</v>
+        <v>569945</v>
       </c>
       <c r="R5" t="n">
-        <v>6957882</v>
+        <v>6957777</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,7 +1041,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ett exemplar har blommat</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128735449</v>
+        <v>128735312</v>
       </c>
       <c r="B6" t="n">
-        <v>91520</v>
+        <v>98651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570013</v>
+        <v>569958</v>
       </c>
       <c r="R6" t="n">
-        <v>6957861</v>
+        <v>6957882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,6 +1143,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2497,37 +2497,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128733844</v>
+        <v>128735562</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2536,10 +2537,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569954</v>
+        <v>569865</v>
       </c>
       <c r="R20" t="n">
-        <v>6958059</v>
+        <v>6957790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2577,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 exemplar har blommat</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2603,7 +2604,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128735562</v>
+        <v>128734344</v>
       </c>
       <c r="B21" t="n">
         <v>57723</v>
@@ -2634,7 +2635,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2643,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569865</v>
+        <v>570110</v>
       </c>
       <c r="R21" t="n">
-        <v>6957790</v>
+        <v>6958034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,38 +2711,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128734344</v>
+        <v>128733844</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>98651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570110</v>
+        <v>569954</v>
       </c>
       <c r="R22" t="n">
-        <v>6958034</v>
+        <v>6958059</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 exemplar har blommat</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3829,10 +3829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128736806</v>
+        <v>128735365</v>
       </c>
       <c r="B33" t="n">
-        <v>91538</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,34 +3840,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569928</v>
+        <v>569970</v>
       </c>
       <c r="R33" t="n">
-        <v>6957738</v>
+        <v>6957886</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3900,6 +3905,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3926,10 +3936,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128735365</v>
+        <v>128736806</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>91538</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,39 +3947,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569970</v>
+        <v>569928</v>
       </c>
       <c r="R34" t="n">
-        <v>6957886</v>
+        <v>6957738</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4002,11 +4007,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128735449</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128735128</v>
+        <v>128734270</v>
       </c>
       <c r="B3" t="n">
         <v>80139</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569944</v>
+        <v>569991</v>
       </c>
       <c r="R3" t="n">
-        <v>6957901</v>
+        <v>6958010</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128734270</v>
+        <v>128735128</v>
       </c>
       <c r="B4" t="n">
         <v>80139</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569991</v>
+        <v>569944</v>
       </c>
       <c r="R4" t="n">
-        <v>6958010</v>
+        <v>6957901</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>128735312</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128735195</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,38 +1484,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128735512</v>
+        <v>128735507</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1524,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569846</v>
+        <v>570013</v>
       </c>
       <c r="R10" t="n">
-        <v>6957795</v>
+        <v>6957861</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,11 +1559,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,37 +1585,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128735507</v>
+        <v>128735512</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1630,10 +1625,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570013</v>
+        <v>569846</v>
       </c>
       <c r="R11" t="n">
-        <v>6957861</v>
+        <v>6957795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,6 +1661,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128736020</v>
+        <v>128735988</v>
       </c>
       <c r="B12" t="n">
-        <v>80139</v>
+        <v>91541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569789</v>
+        <v>569802</v>
       </c>
       <c r="R12" t="n">
-        <v>6957820</v>
+        <v>6957819</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128735988</v>
+        <v>128736020</v>
       </c>
       <c r="B13" t="n">
-        <v>91538</v>
+        <v>80139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569802</v>
+        <v>569789</v>
       </c>
       <c r="R13" t="n">
-        <v>6957819</v>
+        <v>6957820</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2394,7 +2394,7 @@
         <v>128735623</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128733844</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,50 +2817,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128733608</v>
+        <v>128735901</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>91488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569939</v>
+        <v>569825</v>
       </c>
       <c r="R23" t="n">
-        <v>6958006</v>
+        <v>6957814</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,11 +2888,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3031,45 +3021,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128743251</v>
+        <v>128733608</v>
       </c>
       <c r="B25" t="n">
-        <v>97522</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569826</v>
+        <v>569939</v>
       </c>
       <c r="R25" t="n">
-        <v>6957739</v>
+        <v>6958006</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3102,6 +3097,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3128,45 +3128,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128735901</v>
+        <v>128733310</v>
       </c>
       <c r="B26" t="n">
-        <v>91485</v>
+        <v>98656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569825</v>
+        <v>569917</v>
       </c>
       <c r="R26" t="n">
-        <v>6957814</v>
+        <v>6958104</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,49 +3229,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128733310</v>
+        <v>128743251</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>97527</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569917</v>
+        <v>569826</v>
       </c>
       <c r="R27" t="n">
-        <v>6958104</v>
+        <v>6957739</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,7 +3329,7 @@
         <v>128733449</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128733496</v>
       </c>
       <c r="B29" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128734061</v>
+        <v>128737501</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>91541</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,39 +3636,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569997</v>
+        <v>569789</v>
       </c>
       <c r="R31" t="n">
-        <v>6958070</v>
+        <v>6957820</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,11 +3696,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3732,10 +3722,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128737501</v>
+        <v>128734061</v>
       </c>
       <c r="B32" t="n">
-        <v>91538</v>
+        <v>57723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3743,34 +3733,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569789</v>
+        <v>569997</v>
       </c>
       <c r="R32" t="n">
-        <v>6957820</v>
+        <v>6958070</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3803,6 +3798,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3829,10 +3829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128735365</v>
+        <v>128736806</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>91541</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,39 +3840,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569970</v>
+        <v>569928</v>
       </c>
       <c r="R33" t="n">
-        <v>6957886</v>
+        <v>6957738</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3905,11 +3900,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,10 +3926,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128736806</v>
+        <v>128735365</v>
       </c>
       <c r="B34" t="n">
-        <v>91538</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,34 +3937,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569928</v>
+        <v>569970</v>
       </c>
       <c r="R34" t="n">
-        <v>6957738</v>
+        <v>6957886</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4007,6 +4002,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4036,7 +4036,7 @@
         <v>128734237</v>
       </c>
       <c r="B35" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4329,37 +4329,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128734316</v>
+        <v>128737787</v>
       </c>
       <c r="B38" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4368,10 +4369,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569991</v>
+        <v>569763</v>
       </c>
       <c r="R38" t="n">
-        <v>6958010</v>
+        <v>6957837</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4408,7 +4409,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4629,38 +4630,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128737787</v>
+        <v>128734316</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569763</v>
+        <v>569991</v>
       </c>
       <c r="R41" t="n">
-        <v>6957837</v>
+        <v>6958010</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4739,7 +4739,7 @@
         <v>128733519</v>
       </c>
       <c r="B42" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>128743259</v>
       </c>
       <c r="B43" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>128743258</v>
       </c>
       <c r="B46" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128735449</v>
+        <v>128734270</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570013</v>
+        <v>569991</v>
       </c>
       <c r="R2" t="n">
-        <v>6957861</v>
+        <v>6958010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128734270</v>
+        <v>128735128</v>
       </c>
       <c r="B3" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569991</v>
+        <v>569944</v>
       </c>
       <c r="R3" t="n">
-        <v>6958010</v>
+        <v>6957901</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128735128</v>
+        <v>128743260</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>56904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569944</v>
+        <v>569945</v>
       </c>
       <c r="R4" t="n">
-        <v>6957901</v>
+        <v>6957777</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128743260</v>
+        <v>128735449</v>
       </c>
       <c r="B5" t="n">
-        <v>56904</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569945</v>
+        <v>570013</v>
       </c>
       <c r="R5" t="n">
-        <v>6957777</v>
+        <v>6957861</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,7 +1071,7 @@
         <v>128735312</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>128735195</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128734997</v>
       </c>
       <c r="B8" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>128735507</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>128735988</v>
       </c>
       <c r="B12" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,32 +1789,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128736020</v>
+        <v>128734913</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>80169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569789</v>
+        <v>569924</v>
       </c>
       <c r="R13" t="n">
-        <v>6957820</v>
+        <v>6957910</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128734913</v>
+        <v>128736431</v>
       </c>
       <c r="B14" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569924</v>
+        <v>569829</v>
       </c>
       <c r="R14" t="n">
-        <v>6957910</v>
+        <v>6957746</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,32 +1983,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128736431</v>
+        <v>128736020</v>
       </c>
       <c r="B15" t="n">
-        <v>80168</v>
+        <v>80140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569829</v>
+        <v>569789</v>
       </c>
       <c r="R15" t="n">
-        <v>6957746</v>
+        <v>6957820</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2394,7 +2394,7 @@
         <v>128735623</v>
       </c>
       <c r="B19" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128733844</v>
       </c>
       <c r="B22" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>128735901</v>
       </c>
       <c r="B23" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,49 +3128,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128733310</v>
+        <v>128743251</v>
       </c>
       <c r="B26" t="n">
-        <v>98656</v>
+        <v>97530</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569917</v>
+        <v>569826</v>
       </c>
       <c r="R26" t="n">
-        <v>6958104</v>
+        <v>6957739</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3229,45 +3225,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128743251</v>
+        <v>128733310</v>
       </c>
       <c r="B27" t="n">
-        <v>97527</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569826</v>
+        <v>569917</v>
       </c>
       <c r="R27" t="n">
-        <v>6957739</v>
+        <v>6958104</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,7 +3329,7 @@
         <v>128733449</v>
       </c>
       <c r="B28" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128733496</v>
       </c>
       <c r="B29" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128735659</v>
+        <v>128737501</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,21 +3539,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570026</v>
+        <v>569789</v>
       </c>
       <c r="R30" t="n">
-        <v>6957897</v>
+        <v>6957820</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128737501</v>
+        <v>128735659</v>
       </c>
       <c r="B31" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569789</v>
+        <v>570026</v>
       </c>
       <c r="R31" t="n">
-        <v>6957820</v>
+        <v>6957897</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3832,7 +3832,7 @@
         <v>128736806</v>
       </c>
       <c r="B33" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>128734237</v>
       </c>
       <c r="B35" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>128735857</v>
       </c>
       <c r="B36" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4436,45 +4436,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128735254</v>
+        <v>128734316</v>
       </c>
       <c r="B39" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569890</v>
+        <v>569991</v>
       </c>
       <c r="R39" t="n">
-        <v>6957854</v>
+        <v>6958010</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4507,6 +4511,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4533,10 +4542,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128735869</v>
+        <v>128735254</v>
       </c>
       <c r="B40" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4568,10 +4577,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569825</v>
+        <v>569890</v>
       </c>
       <c r="R40" t="n">
-        <v>6957814</v>
+        <v>6957854</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4630,49 +4639,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128734316</v>
+        <v>128735869</v>
       </c>
       <c r="B41" t="n">
-        <v>98656</v>
+        <v>80140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569991</v>
+        <v>569825</v>
       </c>
       <c r="R41" t="n">
-        <v>6958010</v>
+        <v>6957814</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4705,11 +4710,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4739,7 +4739,7 @@
         <v>128733519</v>
       </c>
       <c r="B42" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>128743259</v>
       </c>
       <c r="B43" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128735020</v>
       </c>
       <c r="B44" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>128737653</v>
       </c>
       <c r="B45" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>128743258</v>
       </c>
       <c r="B46" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128734270</v>
+        <v>128735449</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569991</v>
+        <v>570013</v>
       </c>
       <c r="R2" t="n">
-        <v>6958010</v>
+        <v>6957861</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128735128</v>
+        <v>128743260</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>56904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569944</v>
+        <v>569945</v>
       </c>
       <c r="R3" t="n">
-        <v>6957901</v>
+        <v>6957777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128743260</v>
+        <v>128734270</v>
       </c>
       <c r="B4" t="n">
-        <v>56904</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569945</v>
+        <v>569991</v>
       </c>
       <c r="R4" t="n">
-        <v>6957777</v>
+        <v>6958010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735449</v>
+        <v>128735128</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570013</v>
+        <v>569944</v>
       </c>
       <c r="R5" t="n">
-        <v>6957861</v>
+        <v>6957901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1484,37 +1484,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128735507</v>
+        <v>128735512</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1523,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570013</v>
+        <v>569846</v>
       </c>
       <c r="R10" t="n">
-        <v>6957861</v>
+        <v>6957795</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,6 +1560,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1585,38 +1591,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128735512</v>
+        <v>128735507</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1625,10 +1630,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569846</v>
+        <v>570013</v>
       </c>
       <c r="R11" t="n">
-        <v>6957795</v>
+        <v>6957861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,11 +1666,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743248</v>
+        <v>128743249</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569853</v>
+        <v>569769</v>
       </c>
       <c r="R16" t="n">
-        <v>6957734</v>
+        <v>6957830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,7 +2182,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128736601</v>
+        <v>128743248</v>
       </c>
       <c r="B17" t="n">
         <v>57723</v>
@@ -2211,21 +2211,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569845</v>
+        <v>569853</v>
       </c>
       <c r="R17" t="n">
-        <v>6957673</v>
+        <v>6957734</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2257,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2289,10 +2284,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128743249</v>
+        <v>128736601</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,34 +2295,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569769</v>
+        <v>569845</v>
       </c>
       <c r="R18" t="n">
-        <v>6957830</v>
+        <v>6957673</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2817,45 +2817,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128735901</v>
+        <v>128735718</v>
       </c>
       <c r="B23" t="n">
-        <v>91491</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569825</v>
+        <v>569857</v>
       </c>
       <c r="R23" t="n">
-        <v>6957814</v>
+        <v>6957746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2888,6 +2893,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2914,7 +2924,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128735718</v>
+        <v>128733608</v>
       </c>
       <c r="B24" t="n">
         <v>57723</v>
@@ -2954,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569857</v>
+        <v>569939</v>
       </c>
       <c r="R24" t="n">
-        <v>6957746</v>
+        <v>6958006</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,50 +3031,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128733608</v>
+        <v>128735901</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569939</v>
+        <v>569825</v>
       </c>
       <c r="R25" t="n">
-        <v>6958006</v>
+        <v>6957814</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3097,11 +3102,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3128,45 +3128,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128743251</v>
+        <v>128733310</v>
       </c>
       <c r="B26" t="n">
-        <v>97530</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569826</v>
+        <v>569917</v>
       </c>
       <c r="R26" t="n">
-        <v>6957739</v>
+        <v>6958104</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,7 +3229,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128733310</v>
+        <v>128733449</v>
       </c>
       <c r="B27" t="n">
         <v>98659</v>
@@ -3255,7 +3259,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3264,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569917</v>
+        <v>569942</v>
       </c>
       <c r="R27" t="n">
-        <v>6958104</v>
+        <v>6958086</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,49 +3330,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128733449</v>
+        <v>128743251</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>97530</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569942</v>
+        <v>569826</v>
       </c>
       <c r="R28" t="n">
-        <v>6958086</v>
+        <v>6957739</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4329,10 +4329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128737787</v>
+        <v>128735254</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,39 +4340,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569763</v>
+        <v>569890</v>
       </c>
       <c r="R38" t="n">
-        <v>6957837</v>
+        <v>6957854</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4405,11 +4400,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4436,49 +4426,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128734316</v>
+        <v>128735869</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569991</v>
+        <v>569825</v>
       </c>
       <c r="R39" t="n">
-        <v>6958010</v>
+        <v>6957814</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4511,11 +4497,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4542,10 +4523,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128735254</v>
+        <v>128737787</v>
       </c>
       <c r="B40" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4553,34 +4534,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569890</v>
+        <v>569763</v>
       </c>
       <c r="R40" t="n">
-        <v>6957854</v>
+        <v>6957837</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4613,6 +4599,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4639,45 +4630,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128735869</v>
+        <v>128734316</v>
       </c>
       <c r="B41" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569825</v>
+        <v>569991</v>
       </c>
       <c r="R41" t="n">
-        <v>6957814</v>
+        <v>6958010</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4710,6 +4705,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5138,45 +5138,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128743258</v>
+        <v>128735159</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569769</v>
+        <v>569925</v>
       </c>
       <c r="R46" t="n">
-        <v>6957830</v>
+        <v>6957856</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5213,7 +5218,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5240,50 +5245,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128735159</v>
+        <v>128743258</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569925</v>
+        <v>569769</v>
       </c>
       <c r="R47" t="n">
-        <v>6957856</v>
+        <v>6957830</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128735449</v>
+        <v>128734270</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570013</v>
+        <v>569991</v>
       </c>
       <c r="R2" t="n">
-        <v>6957861</v>
+        <v>6958010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128743260</v>
+        <v>128735128</v>
       </c>
       <c r="B3" t="n">
-        <v>56904</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569945</v>
+        <v>569944</v>
       </c>
       <c r="R3" t="n">
-        <v>6957777</v>
+        <v>6957901</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128734270</v>
+        <v>128743260</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>56904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569991</v>
+        <v>569945</v>
       </c>
       <c r="R4" t="n">
-        <v>6958010</v>
+        <v>6957777</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735128</v>
+        <v>128735449</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569944</v>
+        <v>570013</v>
       </c>
       <c r="R5" t="n">
-        <v>6957901</v>
+        <v>6957861</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1484,38 +1484,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128735512</v>
+        <v>128735507</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1524,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569846</v>
+        <v>570013</v>
       </c>
       <c r="R10" t="n">
-        <v>6957795</v>
+        <v>6957861</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,11 +1559,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,37 +1585,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128735507</v>
+        <v>128735512</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1630,10 +1625,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570013</v>
+        <v>569846</v>
       </c>
       <c r="R11" t="n">
-        <v>6957861</v>
+        <v>6957795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,6 +1661,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,32 +1692,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128735988</v>
+        <v>128734913</v>
       </c>
       <c r="B12" t="n">
-        <v>91544</v>
+        <v>80169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569802</v>
+        <v>569924</v>
       </c>
       <c r="R12" t="n">
-        <v>6957819</v>
+        <v>6957910</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128734913</v>
+        <v>128736431</v>
       </c>
       <c r="B13" t="n">
         <v>80169</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569924</v>
+        <v>569829</v>
       </c>
       <c r="R13" t="n">
-        <v>6957910</v>
+        <v>6957746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,32 +1886,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128736431</v>
+        <v>128736020</v>
       </c>
       <c r="B14" t="n">
-        <v>80169</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569829</v>
+        <v>569789</v>
       </c>
       <c r="R14" t="n">
-        <v>6957746</v>
+        <v>6957820</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128736020</v>
+        <v>128735988</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>91544</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569789</v>
+        <v>569802</v>
       </c>
       <c r="R15" t="n">
-        <v>6957820</v>
+        <v>6957819</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2817,50 +2817,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128735718</v>
+        <v>128735901</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569857</v>
+        <v>569825</v>
       </c>
       <c r="R23" t="n">
-        <v>6957746</v>
+        <v>6957814</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,11 +2888,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3031,45 +3021,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128735901</v>
+        <v>128735718</v>
       </c>
       <c r="B25" t="n">
-        <v>91491</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569825</v>
+        <v>569857</v>
       </c>
       <c r="R25" t="n">
-        <v>6957814</v>
+        <v>6957746</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3102,6 +3097,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3229,49 +3229,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128733449</v>
+        <v>128743251</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>97530</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569942</v>
+        <v>569826</v>
       </c>
       <c r="R27" t="n">
-        <v>6958086</v>
+        <v>6957739</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3330,45 +3326,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128743251</v>
+        <v>128733449</v>
       </c>
       <c r="B28" t="n">
-        <v>97530</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569826</v>
+        <v>569942</v>
       </c>
       <c r="R28" t="n">
-        <v>6957739</v>
+        <v>6958086</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4130,45 +4130,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128735857</v>
+        <v>128733359</v>
       </c>
       <c r="B36" t="n">
-        <v>80176</v>
+        <v>57883</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569825</v>
+        <v>569926</v>
       </c>
       <c r="R36" t="n">
-        <v>6957814</v>
+        <v>6958108</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4227,50 +4232,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128733359</v>
+        <v>128735857</v>
       </c>
       <c r="B37" t="n">
-        <v>57883</v>
+        <v>80176</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569926</v>
+        <v>569825</v>
       </c>
       <c r="R37" t="n">
-        <v>6958108</v>
+        <v>6957814</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5138,50 +5138,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128735159</v>
+        <v>128743258</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569925</v>
+        <v>569769</v>
       </c>
       <c r="R46" t="n">
-        <v>6957856</v>
+        <v>6957830</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5218,7 +5213,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5245,45 +5240,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128743258</v>
+        <v>128735159</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569769</v>
+        <v>569925</v>
       </c>
       <c r="R47" t="n">
-        <v>6957830</v>
+        <v>6957856</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128734270</v>
+        <v>128735449</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569991</v>
+        <v>570013</v>
       </c>
       <c r="R2" t="n">
-        <v>6958010</v>
+        <v>6957861</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128735128</v>
+        <v>128734270</v>
       </c>
       <c r="B3" t="n">
         <v>80140</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569944</v>
+        <v>569991</v>
       </c>
       <c r="R3" t="n">
-        <v>6957901</v>
+        <v>6958010</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128743260</v>
+        <v>128735128</v>
       </c>
       <c r="B4" t="n">
-        <v>56904</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569945</v>
+        <v>569944</v>
       </c>
       <c r="R4" t="n">
-        <v>6957777</v>
+        <v>6957901</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,45 +966,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735449</v>
+        <v>128735312</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570013</v>
+        <v>569958</v>
       </c>
       <c r="R5" t="n">
-        <v>6957861</v>
+        <v>6957882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1041,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,49 +1072,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128735312</v>
+        <v>128743260</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>56904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569958</v>
+        <v>569945</v>
       </c>
       <c r="R6" t="n">
-        <v>6957882</v>
+        <v>6957777</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ett exemplar har blommat</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1484,37 +1484,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128735507</v>
+        <v>128735512</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1523,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570013</v>
+        <v>569846</v>
       </c>
       <c r="R10" t="n">
-        <v>6957861</v>
+        <v>6957795</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,6 +1560,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1585,38 +1591,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128735512</v>
+        <v>128735507</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1625,10 +1630,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569846</v>
+        <v>570013</v>
       </c>
       <c r="R11" t="n">
-        <v>6957795</v>
+        <v>6957861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,11 +1666,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,32 +1692,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128734913</v>
+        <v>128735988</v>
       </c>
       <c r="B12" t="n">
-        <v>80169</v>
+        <v>91544</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569924</v>
+        <v>569802</v>
       </c>
       <c r="R12" t="n">
-        <v>6957910</v>
+        <v>6957819</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128736431</v>
+        <v>128734913</v>
       </c>
       <c r="B13" t="n">
         <v>80169</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569829</v>
+        <v>569924</v>
       </c>
       <c r="R13" t="n">
-        <v>6957746</v>
+        <v>6957910</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,32 +1886,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128736020</v>
+        <v>128736431</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>80169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569789</v>
+        <v>569829</v>
       </c>
       <c r="R14" t="n">
-        <v>6957820</v>
+        <v>6957746</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128735988</v>
+        <v>128736020</v>
       </c>
       <c r="B15" t="n">
-        <v>91544</v>
+        <v>80140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569802</v>
+        <v>569789</v>
       </c>
       <c r="R15" t="n">
-        <v>6957819</v>
+        <v>6957820</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743249</v>
+        <v>128743248</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569769</v>
+        <v>569853</v>
       </c>
       <c r="R16" t="n">
-        <v>6957830</v>
+        <v>6957734</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,7 +2182,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128743248</v>
+        <v>128736601</v>
       </c>
       <c r="B17" t="n">
         <v>57723</v>
@@ -2211,16 +2211,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569853</v>
+        <v>569845</v>
       </c>
       <c r="R17" t="n">
-        <v>6957734</v>
+        <v>6957673</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,7 +2262,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2284,10 +2289,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128736601</v>
+        <v>128743249</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2295,39 +2300,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569845</v>
+        <v>569769</v>
       </c>
       <c r="R18" t="n">
-        <v>6957673</v>
+        <v>6957830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,38 +2497,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128735562</v>
+        <v>128733844</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2537,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569865</v>
+        <v>569954</v>
       </c>
       <c r="R20" t="n">
-        <v>6957790</v>
+        <v>6958059</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,7 +2576,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 exemplar har blommat</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2604,7 +2603,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128734344</v>
+        <v>128735562</v>
       </c>
       <c r="B21" t="n">
         <v>57723</v>
@@ -2635,7 +2634,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2644,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570110</v>
+        <v>569865</v>
       </c>
       <c r="R21" t="n">
-        <v>6958034</v>
+        <v>6957790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,37 +2710,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128733844</v>
+        <v>128734344</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569954</v>
+        <v>570110</v>
       </c>
       <c r="R22" t="n">
-        <v>6958059</v>
+        <v>6958034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 exemplar har blommat</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2914,7 +2914,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128733608</v>
+        <v>128735718</v>
       </c>
       <c r="B24" t="n">
         <v>57723</v>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569939</v>
+        <v>569857</v>
       </c>
       <c r="R24" t="n">
-        <v>6958006</v>
+        <v>6957746</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128735718</v>
+        <v>128733608</v>
       </c>
       <c r="B25" t="n">
         <v>57723</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569857</v>
+        <v>569939</v>
       </c>
       <c r="R25" t="n">
-        <v>6957746</v>
+        <v>6958006</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,49 +3128,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128733310</v>
+        <v>128743251</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>97530</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569917</v>
+        <v>569826</v>
       </c>
       <c r="R26" t="n">
-        <v>6958104</v>
+        <v>6957739</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3229,45 +3225,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128743251</v>
+        <v>128733310</v>
       </c>
       <c r="B27" t="n">
-        <v>97530</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569826</v>
+        <v>569917</v>
       </c>
       <c r="R27" t="n">
-        <v>6957739</v>
+        <v>6958104</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128737501</v>
+        <v>128735659</v>
       </c>
       <c r="B30" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,21 +3539,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569789</v>
+        <v>570026</v>
       </c>
       <c r="R30" t="n">
-        <v>6957820</v>
+        <v>6957897</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128735659</v>
+        <v>128737501</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>570026</v>
+        <v>569789</v>
       </c>
       <c r="R31" t="n">
-        <v>6957897</v>
+        <v>6957820</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4130,50 +4130,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128733359</v>
+        <v>128735857</v>
       </c>
       <c r="B36" t="n">
-        <v>57883</v>
+        <v>80176</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569926</v>
+        <v>569825</v>
       </c>
       <c r="R36" t="n">
-        <v>6958108</v>
+        <v>6957814</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,45 +4227,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128735857</v>
+        <v>128733359</v>
       </c>
       <c r="B37" t="n">
-        <v>80176</v>
+        <v>57883</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569825</v>
+        <v>569926</v>
       </c>
       <c r="R37" t="n">
-        <v>6957814</v>
+        <v>6958108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,45 +4329,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128735254</v>
+        <v>128734316</v>
       </c>
       <c r="B38" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569890</v>
+        <v>569991</v>
       </c>
       <c r="R38" t="n">
-        <v>6957854</v>
+        <v>6958010</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,6 +4404,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4426,7 +4435,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128735869</v>
+        <v>128735254</v>
       </c>
       <c r="B39" t="n">
         <v>80140</v>
@@ -4461,10 +4470,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569825</v>
+        <v>569890</v>
       </c>
       <c r="R39" t="n">
-        <v>6957814</v>
+        <v>6957854</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4523,10 +4532,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128737787</v>
+        <v>128735869</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4534,39 +4543,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569763</v>
+        <v>569825</v>
       </c>
       <c r="R40" t="n">
-        <v>6957837</v>
+        <v>6957814</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4599,11 +4603,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4630,37 +4629,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128734316</v>
+        <v>128737787</v>
       </c>
       <c r="B41" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569991</v>
+        <v>569763</v>
       </c>
       <c r="R41" t="n">
-        <v>6958010</v>
+        <v>6957837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5138,45 +5138,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128743258</v>
+        <v>128735159</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569769</v>
+        <v>569925</v>
       </c>
       <c r="R46" t="n">
-        <v>6957830</v>
+        <v>6957856</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5213,7 +5218,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5240,50 +5245,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128735159</v>
+        <v>128743258</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569925</v>
+        <v>569769</v>
       </c>
       <c r="R47" t="n">
-        <v>6957856</v>
+        <v>6957830</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128735449</v>
+        <v>128734270</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570013</v>
+        <v>569991</v>
       </c>
       <c r="R2" t="n">
-        <v>6957861</v>
+        <v>6958010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128734270</v>
+        <v>128735128</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569991</v>
+        <v>569944</v>
       </c>
       <c r="R3" t="n">
-        <v>6958010</v>
+        <v>6957901</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128735128</v>
+        <v>128743260</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>56906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569944</v>
+        <v>569945</v>
       </c>
       <c r="R4" t="n">
-        <v>6957901</v>
+        <v>6957777</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,49 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735312</v>
+        <v>128735449</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569958</v>
+        <v>570013</v>
       </c>
       <c r="R5" t="n">
-        <v>6957882</v>
+        <v>6957861</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128743260</v>
+        <v>128735312</v>
       </c>
       <c r="B6" t="n">
-        <v>56904</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569945</v>
+        <v>569958</v>
       </c>
       <c r="R6" t="n">
-        <v>6957777</v>
+        <v>6957882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,7 +1177,7 @@
         <v>128735195</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128734997</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128735394</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,38 +1484,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128735512</v>
+        <v>128735507</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1524,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569846</v>
+        <v>570013</v>
       </c>
       <c r="R10" t="n">
-        <v>6957795</v>
+        <v>6957861</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,11 +1559,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,37 +1585,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128735507</v>
+        <v>128735512</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1630,10 +1625,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570013</v>
+        <v>569846</v>
       </c>
       <c r="R11" t="n">
-        <v>6957861</v>
+        <v>6957795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,6 +1661,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,7 +1695,7 @@
         <v>128735988</v>
       </c>
       <c r="B12" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>128734913</v>
       </c>
       <c r="B13" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>128736431</v>
       </c>
       <c r="B14" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128736020</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743248</v>
+        <v>128743249</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569853</v>
+        <v>569769</v>
       </c>
       <c r="R16" t="n">
-        <v>6957734</v>
+        <v>6957830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,10 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128736601</v>
+        <v>128743248</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2211,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569845</v>
+        <v>569853</v>
       </c>
       <c r="R17" t="n">
-        <v>6957673</v>
+        <v>6957734</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2257,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2289,10 +2284,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128743249</v>
+        <v>128736601</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,34 +2295,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569769</v>
+        <v>569845</v>
       </c>
       <c r="R18" t="n">
-        <v>6957830</v>
+        <v>6957673</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,7 +2394,7 @@
         <v>128735623</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2497,37 +2497,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128733844</v>
+        <v>128735562</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2536,10 +2537,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569954</v>
+        <v>569865</v>
       </c>
       <c r="R20" t="n">
-        <v>6958059</v>
+        <v>6957790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2577,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 exemplar har blommat</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2603,10 +2604,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128735562</v>
+        <v>128734344</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,7 +2635,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2643,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569865</v>
+        <v>570110</v>
       </c>
       <c r="R21" t="n">
-        <v>6957790</v>
+        <v>6958034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,38 +2711,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128734344</v>
+        <v>128733844</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570110</v>
+        <v>569954</v>
       </c>
       <c r="R22" t="n">
-        <v>6958034</v>
+        <v>6958059</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 exemplar har blommat</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2820,7 +2820,7 @@
         <v>128735901</v>
       </c>
       <c r="B23" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>128735718</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128733608</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>128743251</v>
       </c>
       <c r="B26" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>128733310</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>128733449</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128733496</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128735659</v>
+        <v>128737501</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>91551</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,21 +3539,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>570026</v>
+        <v>569789</v>
       </c>
       <c r="R30" t="n">
-        <v>6957897</v>
+        <v>6957820</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128737501</v>
+        <v>128735659</v>
       </c>
       <c r="B31" t="n">
-        <v>91544</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569789</v>
+        <v>570026</v>
       </c>
       <c r="R31" t="n">
-        <v>6957820</v>
+        <v>6957897</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3725,7 +3725,7 @@
         <v>128734061</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3829,10 +3829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128736806</v>
+        <v>128735365</v>
       </c>
       <c r="B33" t="n">
-        <v>91544</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,34 +3840,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569928</v>
+        <v>569970</v>
       </c>
       <c r="R33" t="n">
-        <v>6957738</v>
+        <v>6957886</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3900,6 +3905,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3926,10 +3936,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128735365</v>
+        <v>128736806</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>91551</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,39 +3947,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569970</v>
+        <v>569928</v>
       </c>
       <c r="R34" t="n">
-        <v>6957886</v>
+        <v>6957738</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4002,11 +4007,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4036,7 +4036,7 @@
         <v>128734237</v>
       </c>
       <c r="B35" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>128735857</v>
       </c>
       <c r="B36" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>128733359</v>
       </c>
       <c r="B37" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>128734316</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>128735254</v>
       </c>
       <c r="B39" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>128735869</v>
       </c>
       <c r="B40" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>128737787</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>128733519</v>
       </c>
       <c r="B42" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>128743259</v>
       </c>
       <c r="B43" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128735020</v>
       </c>
       <c r="B44" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>128737653</v>
       </c>
       <c r="B45" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>128735159</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>128743258</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>128733395</v>
       </c>
       <c r="B48" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>128736388</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743249</v>
+        <v>128743248</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569769</v>
+        <v>569853</v>
       </c>
       <c r="R16" t="n">
-        <v>6957830</v>
+        <v>6957734</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,7 +2182,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128743248</v>
+        <v>128736601</v>
       </c>
       <c r="B17" t="n">
         <v>57725</v>
@@ -2211,16 +2211,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569853</v>
+        <v>569845</v>
       </c>
       <c r="R17" t="n">
-        <v>6957734</v>
+        <v>6957673</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,7 +2262,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2284,10 +2289,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128736601</v>
+        <v>128743249</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2295,39 +2300,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569845</v>
+        <v>569769</v>
       </c>
       <c r="R18" t="n">
-        <v>6957673</v>
+        <v>6957830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2817,45 +2817,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128735901</v>
+        <v>128733310</v>
       </c>
       <c r="B23" t="n">
-        <v>91497</v>
+        <v>98669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569825</v>
+        <v>569917</v>
       </c>
       <c r="R23" t="n">
-        <v>6957814</v>
+        <v>6958104</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2914,38 +2918,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128735718</v>
+        <v>128733449</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2954,10 +2957,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569857</v>
+        <v>569942</v>
       </c>
       <c r="R24" t="n">
-        <v>6957746</v>
+        <v>6958086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,11 +2993,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3021,50 +3019,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128733608</v>
+        <v>128743251</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>97540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569939</v>
+        <v>569826</v>
       </c>
       <c r="R25" t="n">
-        <v>6958006</v>
+        <v>6957739</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3097,11 +3090,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3128,10 +3116,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128743251</v>
+        <v>128735901</v>
       </c>
       <c r="B26" t="n">
-        <v>97540</v>
+        <v>91497</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,21 +3127,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3151,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569826</v>
+        <v>569825</v>
       </c>
       <c r="R26" t="n">
-        <v>6957739</v>
+        <v>6957814</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,37 +3213,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128733310</v>
+        <v>128735718</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3264,10 +3253,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569917</v>
+        <v>569857</v>
       </c>
       <c r="R27" t="n">
-        <v>6958104</v>
+        <v>6957746</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3300,6 +3289,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3326,37 +3320,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128733449</v>
+        <v>128733608</v>
       </c>
       <c r="B28" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3365,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569942</v>
+        <v>569939</v>
       </c>
       <c r="R28" t="n">
-        <v>6958086</v>
+        <v>6958006</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3401,6 +3396,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4329,49 +4329,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128734316</v>
+        <v>128735254</v>
       </c>
       <c r="B38" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569991</v>
+        <v>569890</v>
       </c>
       <c r="R38" t="n">
-        <v>6958010</v>
+        <v>6957854</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4404,11 +4400,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4435,7 +4426,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128735254</v>
+        <v>128735869</v>
       </c>
       <c r="B39" t="n">
         <v>80144</v>
@@ -4470,10 +4461,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569890</v>
+        <v>569825</v>
       </c>
       <c r="R39" t="n">
-        <v>6957854</v>
+        <v>6957814</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4532,10 +4523,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128735869</v>
+        <v>128737787</v>
       </c>
       <c r="B40" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4543,34 +4534,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569825</v>
+        <v>569763</v>
       </c>
       <c r="R40" t="n">
-        <v>6957814</v>
+        <v>6957837</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4603,6 +4599,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4629,38 +4630,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128737787</v>
+        <v>128734316</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569763</v>
+        <v>569991</v>
       </c>
       <c r="R41" t="n">
-        <v>6957837</v>
+        <v>6958010</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743248</v>
+        <v>128743249</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569853</v>
+        <v>569769</v>
       </c>
       <c r="R16" t="n">
-        <v>6957734</v>
+        <v>6957830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,7 +2182,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128736601</v>
+        <v>128743248</v>
       </c>
       <c r="B17" t="n">
         <v>57725</v>
@@ -2211,21 +2211,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569845</v>
+        <v>569853</v>
       </c>
       <c r="R17" t="n">
-        <v>6957673</v>
+        <v>6957734</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2257,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2289,10 +2284,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128743249</v>
+        <v>128736601</v>
       </c>
       <c r="B18" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,34 +2295,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569769</v>
+        <v>569845</v>
       </c>
       <c r="R18" t="n">
-        <v>6957830</v>
+        <v>6957673</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2817,49 +2817,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128733310</v>
+        <v>128735901</v>
       </c>
       <c r="B23" t="n">
-        <v>98669</v>
+        <v>91497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569917</v>
+        <v>569825</v>
       </c>
       <c r="R23" t="n">
-        <v>6958104</v>
+        <v>6957814</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,37 +2914,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128733449</v>
+        <v>128735718</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2957,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569942</v>
+        <v>569857</v>
       </c>
       <c r="R24" t="n">
-        <v>6958086</v>
+        <v>6957746</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2993,6 +2990,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3019,45 +3021,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128743251</v>
+        <v>128733608</v>
       </c>
       <c r="B25" t="n">
-        <v>97540</v>
+        <v>57725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569826</v>
+        <v>569939</v>
       </c>
       <c r="R25" t="n">
-        <v>6957739</v>
+        <v>6958006</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3090,6 +3097,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3116,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128735901</v>
+        <v>128743251</v>
       </c>
       <c r="B26" t="n">
-        <v>91497</v>
+        <v>97540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3127,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3151,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569825</v>
+        <v>569826</v>
       </c>
       <c r="R26" t="n">
-        <v>6957814</v>
+        <v>6957739</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3213,38 +3225,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128735718</v>
+        <v>128733310</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3253,10 +3264,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569857</v>
+        <v>569917</v>
       </c>
       <c r="R27" t="n">
-        <v>6957746</v>
+        <v>6958104</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3289,11 +3300,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3320,38 +3326,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128733608</v>
+        <v>128733449</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3360,10 +3365,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569939</v>
+        <v>569942</v>
       </c>
       <c r="R28" t="n">
-        <v>6958006</v>
+        <v>6958086</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3396,11 +3401,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128734270</v>
+        <v>128735449</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569991</v>
+        <v>570013</v>
       </c>
       <c r="R2" t="n">
-        <v>6958010</v>
+        <v>6957861</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128735128</v>
+        <v>128735312</v>
       </c>
       <c r="B3" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569944</v>
+        <v>569958</v>
       </c>
       <c r="R3" t="n">
-        <v>6957901</v>
+        <v>6957882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +881,7 @@
         <v>128743260</v>
       </c>
       <c r="B4" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128735449</v>
+        <v>128734270</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +991,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570013</v>
+        <v>569991</v>
       </c>
       <c r="R5" t="n">
-        <v>6957861</v>
+        <v>6958010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,49 +1077,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128735312</v>
+        <v>128735128</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569958</v>
+        <v>569944</v>
       </c>
       <c r="R6" t="n">
-        <v>6957882</v>
+        <v>6957901</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,11 +1148,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,7 +1177,7 @@
         <v>128735195</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128734997</v>
       </c>
       <c r="B8" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128735394</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,37 +1484,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128735507</v>
+        <v>128735512</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1523,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570013</v>
+        <v>569846</v>
       </c>
       <c r="R10" t="n">
-        <v>6957861</v>
+        <v>6957795</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,6 +1560,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1585,38 +1591,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128735512</v>
+        <v>128735507</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1625,10 +1630,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569846</v>
+        <v>570013</v>
       </c>
       <c r="R11" t="n">
-        <v>6957795</v>
+        <v>6957861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,11 +1666,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,32 +1692,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128735988</v>
+        <v>128734913</v>
       </c>
       <c r="B12" t="n">
-        <v>91551</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569802</v>
+        <v>569924</v>
       </c>
       <c r="R12" t="n">
-        <v>6957819</v>
+        <v>6957910</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128734913</v>
+        <v>128736431</v>
       </c>
       <c r="B13" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569924</v>
+        <v>569829</v>
       </c>
       <c r="R13" t="n">
-        <v>6957910</v>
+        <v>6957746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,32 +1886,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128736431</v>
+        <v>128736020</v>
       </c>
       <c r="B14" t="n">
-        <v>80173</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569829</v>
+        <v>569789</v>
       </c>
       <c r="R14" t="n">
-        <v>6957746</v>
+        <v>6957820</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128736020</v>
+        <v>128735988</v>
       </c>
       <c r="B15" t="n">
-        <v>80144</v>
+        <v>91560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569789</v>
+        <v>569802</v>
       </c>
       <c r="R15" t="n">
-        <v>6957820</v>
+        <v>6957819</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743249</v>
+        <v>128743248</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569769</v>
+        <v>569853</v>
       </c>
       <c r="R16" t="n">
-        <v>6957830</v>
+        <v>6957734</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,10 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128743248</v>
+        <v>128736601</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,16 +2211,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569853</v>
+        <v>569845</v>
       </c>
       <c r="R17" t="n">
-        <v>6957734</v>
+        <v>6957673</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,7 +2262,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2284,10 +2289,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128736601</v>
+        <v>128743249</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2295,39 +2300,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569845</v>
+        <v>569769</v>
       </c>
       <c r="R18" t="n">
-        <v>6957673</v>
+        <v>6957830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,7 +2394,7 @@
         <v>128735623</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>128735562</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>128734344</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>128733844</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,45 +2817,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128735901</v>
+        <v>128735718</v>
       </c>
       <c r="B23" t="n">
-        <v>91497</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569825</v>
+        <v>569857</v>
       </c>
       <c r="R23" t="n">
-        <v>6957814</v>
+        <v>6957746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2888,6 +2893,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2914,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128735718</v>
+        <v>128733608</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569857</v>
+        <v>569939</v>
       </c>
       <c r="R24" t="n">
-        <v>6957746</v>
+        <v>6958006</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,38 +3031,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128733608</v>
+        <v>128733310</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3061,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569939</v>
+        <v>569917</v>
       </c>
       <c r="R25" t="n">
-        <v>6958006</v>
+        <v>6958104</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3097,11 +3106,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3128,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128743251</v>
+        <v>128735901</v>
       </c>
       <c r="B26" t="n">
-        <v>97540</v>
+        <v>91506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,21 +3143,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569826</v>
+        <v>569825</v>
       </c>
       <c r="R26" t="n">
-        <v>6957739</v>
+        <v>6957814</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3229,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128733310</v>
+        <v>128733449</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,7 +3259,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3264,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569917</v>
+        <v>569942</v>
       </c>
       <c r="R27" t="n">
-        <v>6958104</v>
+        <v>6958086</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,49 +3330,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128733449</v>
+        <v>128743251</v>
       </c>
       <c r="B28" t="n">
-        <v>98669</v>
+        <v>97549</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569942</v>
+        <v>569826</v>
       </c>
       <c r="R28" t="n">
-        <v>6958086</v>
+        <v>6957739</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
         <v>128733496</v>
       </c>
       <c r="B29" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128737501</v>
+        <v>128734061</v>
       </c>
       <c r="B30" t="n">
-        <v>91551</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,34 +3539,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569789</v>
+        <v>569997</v>
       </c>
       <c r="R30" t="n">
-        <v>6957820</v>
+        <v>6958070</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3599,6 +3604,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3625,10 +3635,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128735659</v>
+        <v>128737501</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3646,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3660,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>570026</v>
+        <v>569789</v>
       </c>
       <c r="R31" t="n">
-        <v>6957897</v>
+        <v>6957820</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3722,10 +3732,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128734061</v>
+        <v>128735659</v>
       </c>
       <c r="B32" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3733,39 +3743,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569997</v>
+        <v>570026</v>
       </c>
       <c r="R32" t="n">
-        <v>6958070</v>
+        <v>6957897</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3798,11 +3803,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3829,10 +3829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128735365</v>
+        <v>128736806</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>91560</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,39 +3840,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569970</v>
+        <v>569928</v>
       </c>
       <c r="R33" t="n">
-        <v>6957886</v>
+        <v>6957738</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3905,11 +3900,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3936,10 +3926,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128736806</v>
+        <v>128735365</v>
       </c>
       <c r="B34" t="n">
-        <v>91551</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,34 +3937,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569928</v>
+        <v>569970</v>
       </c>
       <c r="R34" t="n">
-        <v>6957738</v>
+        <v>6957886</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4007,6 +4002,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4036,7 +4036,7 @@
         <v>128734237</v>
       </c>
       <c r="B35" t="n">
-        <v>97540</v>
+        <v>97549</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>128735857</v>
       </c>
       <c r="B36" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>128733359</v>
       </c>
       <c r="B37" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>128735254</v>
       </c>
       <c r="B38" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>128735869</v>
       </c>
       <c r="B39" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4523,38 +4523,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128737787</v>
+        <v>128734316</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4563,10 +4562,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569763</v>
+        <v>569991</v>
       </c>
       <c r="R40" t="n">
-        <v>6957837</v>
+        <v>6958010</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4603,7 +4602,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4630,37 +4629,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128734316</v>
+        <v>128737787</v>
       </c>
       <c r="B41" t="n">
-        <v>98669</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569991</v>
+        <v>569763</v>
       </c>
       <c r="R41" t="n">
-        <v>6958010</v>
+        <v>6957837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4739,7 +4739,7 @@
         <v>128733519</v>
       </c>
       <c r="B42" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>128743259</v>
       </c>
       <c r="B43" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>128735020</v>
       </c>
       <c r="B44" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>128737653</v>
       </c>
       <c r="B45" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>128735159</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>128743258</v>
       </c>
       <c r="B47" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>128733395</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>128736388</v>
       </c>
       <c r="B49" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 39116-2025 artfynd.xlsx
+++ b/artfynd/A 39116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128735449</v>
+        <v>128743260</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>56908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570013</v>
+        <v>569945</v>
       </c>
       <c r="R2" t="n">
-        <v>6957861</v>
+        <v>6957777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,49 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128735312</v>
+        <v>128735449</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569958</v>
+        <v>570013</v>
       </c>
       <c r="R3" t="n">
-        <v>6957882</v>
+        <v>6957861</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128743260</v>
+        <v>128734270</v>
       </c>
       <c r="B4" t="n">
-        <v>56908</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569945</v>
+        <v>569991</v>
       </c>
       <c r="R4" t="n">
-        <v>6957777</v>
+        <v>6958010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128734270</v>
+        <v>128735128</v>
       </c>
       <c r="B5" t="n">
         <v>80146</v>
@@ -1015,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569991</v>
+        <v>569944</v>
       </c>
       <c r="R5" t="n">
-        <v>6958010</v>
+        <v>6957901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128735128</v>
+        <v>128735312</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569944</v>
+        <v>569958</v>
       </c>
       <c r="R6" t="n">
-        <v>6957901</v>
+        <v>6957882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,6 +1143,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ett exemplar har blommat</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1484,38 +1484,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128735512</v>
+        <v>128735507</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1524,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569846</v>
+        <v>570013</v>
       </c>
       <c r="R10" t="n">
-        <v>6957795</v>
+        <v>6957861</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,11 +1559,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,37 +1585,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128735507</v>
+        <v>128735512</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1630,10 +1625,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570013</v>
+        <v>569846</v>
       </c>
       <c r="R11" t="n">
-        <v>6957861</v>
+        <v>6957795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,6 +1661,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,32 +1692,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128734913</v>
+        <v>128735988</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>91560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569924</v>
+        <v>569802</v>
       </c>
       <c r="R12" t="n">
-        <v>6957910</v>
+        <v>6957819</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128736431</v>
+        <v>128734913</v>
       </c>
       <c r="B13" t="n">
         <v>80175</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569829</v>
+        <v>569924</v>
       </c>
       <c r="R13" t="n">
-        <v>6957746</v>
+        <v>6957910</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,32 +1886,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128736020</v>
+        <v>128736431</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569789</v>
+        <v>569829</v>
       </c>
       <c r="R14" t="n">
-        <v>6957820</v>
+        <v>6957746</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128735988</v>
+        <v>128736020</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569802</v>
+        <v>569789</v>
       </c>
       <c r="R15" t="n">
-        <v>6957819</v>
+        <v>6957820</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128743248</v>
+        <v>128743249</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569853</v>
+        <v>569769</v>
       </c>
       <c r="R16" t="n">
-        <v>6957734</v>
+        <v>6957830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
+          <t>Lockläte, övriga läten</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2182,7 +2182,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128736601</v>
+        <v>128743248</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2211,21 +2211,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569845</v>
+        <v>569853</v>
       </c>
       <c r="R17" t="n">
-        <v>6957673</v>
+        <v>6957734</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2257,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall. Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2289,10 +2284,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128743249</v>
+        <v>128736601</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,34 +2295,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569769</v>
+        <v>569845</v>
       </c>
       <c r="R18" t="n">
-        <v>6957830</v>
+        <v>6957673</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Lockläte, övriga läten</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2817,38 +2817,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128735718</v>
+        <v>128733310</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2857,10 +2856,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569857</v>
+        <v>569917</v>
       </c>
       <c r="R23" t="n">
-        <v>6957746</v>
+        <v>6958104</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,11 +2892,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2924,50 +2918,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128733608</v>
+        <v>128735901</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569939</v>
+        <v>569825</v>
       </c>
       <c r="R24" t="n">
-        <v>6958006</v>
+        <v>6957814</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3000,11 +2989,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3031,37 +3015,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128733310</v>
+        <v>128735718</v>
       </c>
       <c r="B25" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3070,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569917</v>
+        <v>569857</v>
       </c>
       <c r="R25" t="n">
-        <v>6958104</v>
+        <v>6957746</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3106,6 +3091,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3132,45 +3122,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128735901</v>
+        <v>128733608</v>
       </c>
       <c r="B26" t="n">
-        <v>91506</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569825</v>
+        <v>569939</v>
       </c>
       <c r="R26" t="n">
-        <v>6957814</v>
+        <v>6958006</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3203,6 +3198,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3229,49 +3229,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128733449</v>
+        <v>128743251</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>97549</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569942</v>
+        <v>569826</v>
       </c>
       <c r="R27" t="n">
-        <v>6958086</v>
+        <v>6957739</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3330,45 +3326,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128743251</v>
+        <v>128733449</v>
       </c>
       <c r="B28" t="n">
-        <v>97549</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569826</v>
+        <v>569942</v>
       </c>
       <c r="R28" t="n">
-        <v>6957739</v>
+        <v>6958086</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128734061</v>
+        <v>128737501</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,39 +3539,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569997</v>
+        <v>569789</v>
       </c>
       <c r="R30" t="n">
-        <v>6958070</v>
+        <v>6957820</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3604,11 +3599,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3635,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128737501</v>
+        <v>128735659</v>
       </c>
       <c r="B31" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3646,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3670,10 +3660,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569789</v>
+        <v>570026</v>
       </c>
       <c r="R31" t="n">
-        <v>6957820</v>
+        <v>6957897</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3732,10 +3722,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128735659</v>
+        <v>128734061</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3743,34 +3733,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>570026</v>
+        <v>569997</v>
       </c>
       <c r="R32" t="n">
-        <v>6957897</v>
+        <v>6958070</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3803,6 +3798,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på död tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3829,10 +3829,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128736806</v>
+        <v>128735365</v>
       </c>
       <c r="B33" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,34 +3840,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569928</v>
+        <v>569970</v>
       </c>
       <c r="R33" t="n">
-        <v>6957738</v>
+        <v>6957886</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3900,6 +3905,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3926,10 +3936,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128735365</v>
+        <v>128736806</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,39 +3947,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569970</v>
+        <v>569928</v>
       </c>
       <c r="R34" t="n">
-        <v>6957886</v>
+        <v>6957738</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4002,11 +4007,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4130,45 +4130,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128735857</v>
+        <v>128733359</v>
       </c>
       <c r="B36" t="n">
-        <v>80182</v>
+        <v>57887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569825</v>
+        <v>569926</v>
       </c>
       <c r="R36" t="n">
-        <v>6957814</v>
+        <v>6958108</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4227,50 +4232,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128733359</v>
+        <v>128735857</v>
       </c>
       <c r="B37" t="n">
-        <v>57887</v>
+        <v>80182</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storstensjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569926</v>
+        <v>569825</v>
       </c>
       <c r="R37" t="n">
-        <v>6958108</v>
+        <v>6957814</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4523,37 +4523,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128734316</v>
+        <v>128737787</v>
       </c>
       <c r="B40" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4562,10 +4563,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569991</v>
+        <v>569763</v>
       </c>
       <c r="R40" t="n">
-        <v>6958010</v>
+        <v>6957837</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4602,7 +4603,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Kan finnas mer I mossan och blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4629,38 +4630,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128737787</v>
+        <v>128734316</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569763</v>
+        <v>569991</v>
       </c>
       <c r="R41" t="n">
-        <v>6957837</v>
+        <v>6958010</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer I mossan och blåbärsriset</t>
         </is>
       </c>
       <c r="AD41" t="b">
